--- a/public/plantilla-ats.xlsx
+++ b/public/plantilla-ats.xlsx
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="F59" s="63">
-        <f>H5</f>
+        <f>I5</f>
         <v/>
       </c>
     </row>

--- a/public/plantilla-ats.xlsx
+++ b/public/plantilla-ats.xlsx
@@ -3,19 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATS" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="27">
+  <fonts count="39">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,14 +75,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="Arial"/>
       <family val="2"/>
       <b val="1"/>
@@ -165,14 +157,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <sz val="9.5"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="0"/>
-      <sz val="8.5"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -212,19 +196,114 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color theme="0" tint="-0.249977111117893"/>
+      <sz val="7"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF404040"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF1B2A45"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="8.5"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -236,18 +315,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2F75B5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2F75B5"/>
-        <bgColor rgb="FF003366"/>
       </patternFill>
     </fill>
     <fill>
@@ -270,24 +337,84 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F75B5"/>
+        <fgColor theme="0" tint="-0.0499893185216834"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B1F33"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B1F33"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5A018"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5A018"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5A018"/>
+        <bgColor rgb="FFEEF1F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF3"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF3"/>
         <bgColor rgb="FFEEF1F6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.0499893185216834"/>
-        <bgColor rgb="FF003366"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCCF6A"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="50">
     <border>
       <left/>
       <right/>
@@ -417,19 +544,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </top>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -523,26 +637,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -570,12 +664,276 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF0B1F33"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF0B1F33"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
         <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF0B1F33"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -584,7 +942,75 @@
         <color theme="3" tint="0.5999633777886288"/>
       </right>
       <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
         <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -598,298 +1024,911 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="9" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="30" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="12" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -899,7 +1938,154 @@
     <cellStyle name="Normal 4" xfId="4"/>
     <cellStyle name="Normal 6 2" xfId="5"/>
   </cellStyles>
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00A651"/>
+          <bgColor rgb="FF00A651"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC00000"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF595959"/>
+          <bgColor rgb="FF595959"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7F4F24"/>
+          <bgColor rgb="FF7F4F24"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7030A0"/>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF57C00"/>
+          <bgColor rgb="FFF57C00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00A651"/>
+          <bgColor rgb="FF00A651"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0070C0"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC00000"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors/>
 </styleSheet>
 </file>
 
@@ -914,9 +2100,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>131445</xdr:rowOff>
+      <xdr:colOff>1189291</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>177646</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -932,7 +2118,7 @@
       <xdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
-          <a:ext cx="2644140" cy="1259205"/>
+          <a:ext cx="3456000" cy="1692000"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
@@ -1248,1213 +2434,1247 @@
     <tabColor theme="4" tint="0.3999755851924192"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col width="5" customWidth="1" style="70" min="1" max="1"/>
-    <col width="28" customWidth="1" style="70" min="2" max="2"/>
-    <col width="24" customWidth="1" style="70" min="3" max="4"/>
-    <col width="10.77734375" customWidth="1" style="70" min="5" max="7"/>
-    <col width="40" customWidth="1" style="70" min="8" max="8"/>
-    <col width="16" customWidth="1" style="70" min="9" max="9"/>
-    <col width="11" customWidth="1" style="70" min="10" max="10"/>
-    <col width="8.88671875" customWidth="1" style="70" min="11" max="16384"/>
+    <col width="5" customWidth="1" style="127" min="1" max="1"/>
+    <col width="28" customWidth="1" style="127" min="2" max="2"/>
+    <col width="24" customWidth="1" style="127" min="3" max="4"/>
+    <col width="10.77734375" customWidth="1" style="127" min="5" max="7"/>
+    <col width="40" customWidth="1" style="127" min="8" max="8"/>
+    <col width="15.77734375" customWidth="1" style="127" min="9" max="9"/>
+    <col width="15.77734375" customWidth="1" style="127" min="10" max="10"/>
+    <col width="11" customWidth="1" style="127" min="11" max="11"/>
+    <col width="8.88671875" customWidth="1" style="127" min="12" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.05" customHeight="1" s="70">
-      <c r="D1" s="35" t="inlineStr">
+    <row r="1" ht="40.05" customHeight="1" s="127">
+      <c r="D1" s="133" t="inlineStr">
         <is>
           <t>ANÁLISIS DE TRABAJO SEGURO (ATS)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="14.4" customHeight="1" s="70">
-      <c r="D2" s="37" t="n"/>
-      <c r="E2" s="38" t="n"/>
-      <c r="F2" s="38" t="n"/>
-      <c r="G2" s="38" t="n"/>
-      <c r="H2" s="38" t="n"/>
-      <c r="I2" s="38" t="n"/>
-      <c r="J2" s="38" t="n"/>
-    </row>
-    <row r="3" ht="4.95" customHeight="1" s="70">
-      <c r="D3" s="75" t="n"/>
-      <c r="E3" s="56" t="n"/>
-      <c r="F3" s="56" t="n"/>
-      <c r="G3" s="56" t="n"/>
-      <c r="H3" s="56" t="n"/>
-      <c r="I3" s="56" t="n"/>
-      <c r="J3" s="56" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="70">
-      <c r="H4" s="53" t="inlineStr">
+    <row r="2" ht="14.4" customHeight="1" s="127">
+      <c r="D2" s="96" t="n"/>
+      <c r="E2" s="98" t="n"/>
+      <c r="F2" s="98" t="n"/>
+      <c r="G2" s="98" t="n"/>
+      <c r="H2" s="98" t="n"/>
+      <c r="I2" s="98" t="n"/>
+      <c r="J2" s="98" t="n"/>
+      <c r="K2" s="98" t="n"/>
+    </row>
+    <row r="3" ht="4.95" customHeight="1" s="127">
+      <c r="D3" s="60" t="n"/>
+      <c r="E3" s="104" t="n"/>
+      <c r="F3" s="104" t="n"/>
+      <c r="G3" s="104" t="n"/>
+      <c r="H3" s="104" t="n"/>
+      <c r="I3" s="104" t="n"/>
+      <c r="J3" s="104" t="n"/>
+      <c r="K3" s="104" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="127">
+      <c r="D4" s="192" t="n"/>
+      <c r="H4" s="92" t="n"/>
+      <c r="I4" s="139" t="inlineStr">
         <is>
           <t>CONTROL DOCUMENTAL</t>
         </is>
       </c>
-      <c r="I4" s="30" t="n"/>
-      <c r="J4" s="31" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="70">
-      <c r="D5" s="40" t="inlineStr">
+      <c r="J4" s="93" t="n"/>
+      <c r="K4" s="89" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="127">
+      <c r="D5" s="99" t="inlineStr">
         <is>
           <t>REFORMAS Y REMODELACIONES</t>
         </is>
       </c>
-      <c r="G5" s="41" t="n"/>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="92" t="n"/>
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="I5" s="49" t="inlineStr">
+      <c r="J5" s="64" t="inlineStr">
         <is>
           <t>RYR-SS-008</t>
         </is>
       </c>
-      <c r="J5" s="31" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="70">
-      <c r="D6" s="44" t="inlineStr">
+      <c r="K5" s="89" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="127">
+      <c r="D6" s="90" t="inlineStr">
         <is>
           <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN.</t>
         </is>
       </c>
-      <c r="G6" s="41" t="n"/>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="92" t="n"/>
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
       </c>
-      <c r="I6" s="49" t="n">
+      <c r="J6" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="31" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="70">
-      <c r="D7" s="80" t="n"/>
-      <c r="E7" s="80" t="n"/>
-      <c r="F7" s="80" t="n"/>
-      <c r="G7" s="81" t="n"/>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="K6" s="89" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="127">
+      <c r="D7" s="194" t="n"/>
+      <c r="H7" s="92" t="n"/>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="I7" s="49" t="inlineStr">
+      <c r="J7" s="64" t="inlineStr">
         <is>
           <t>04/10/2026</t>
         </is>
       </c>
-      <c r="J7" s="31" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="70">
-      <c r="D8" s="66" t="n"/>
-      <c r="E8" s="66" t="n"/>
-      <c r="F8" s="66" t="n"/>
-      <c r="G8" s="81" t="n"/>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="K7" s="89" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="127">
+      <c r="D8" s="194" t="n"/>
+      <c r="H8" s="92" t="n"/>
+      <c r="I8" s="254" t="inlineStr">
         <is>
           <t>Página</t>
         </is>
       </c>
-      <c r="I8" s="49" t="inlineStr">
+      <c r="J8" s="58" t="inlineStr">
         <is>
           <t>1 de 2</t>
         </is>
       </c>
-      <c r="J8" s="31" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="70">
-      <c r="A9" s="103" t="inlineStr">
+      <c r="K8" s="94" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="127">
+      <c r="A9" s="287" t="inlineStr">
         <is>
           <t>Paso a paso de la tarea, peligros, riesgos y controles, acordados con el equipo antes de empezar · Decreto 1072 de 2015</t>
         </is>
       </c>
-      <c r="B9" s="115" t="n"/>
-      <c r="C9" s="115" t="n"/>
-      <c r="D9" s="115" t="n"/>
-      <c r="E9" s="115" t="n"/>
-      <c r="F9" s="115" t="n"/>
-      <c r="G9" s="115" t="n"/>
-      <c r="H9" s="115" t="n"/>
-      <c r="I9" s="115" t="n"/>
-      <c r="J9" s="116" t="n"/>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" s="70">
-      <c r="A10" s="54" t="inlineStr">
+      <c r="B9" s="347" t="n"/>
+      <c r="C9" s="347" t="n"/>
+      <c r="D9" s="347" t="n"/>
+      <c r="E9" s="347" t="n"/>
+      <c r="F9" s="347" t="n"/>
+      <c r="G9" s="347" t="n"/>
+      <c r="H9" s="347" t="n"/>
+      <c r="I9" s="347" t="n"/>
+      <c r="J9" s="347" t="n"/>
+      <c r="K9" s="352" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="127">
+      <c r="A10" s="137" t="inlineStr">
         <is>
           <t>1. DATOS DE LA TAREA</t>
         </is>
       </c>
-      <c r="B10" s="38" t="n"/>
-      <c r="C10" s="38" t="n"/>
-      <c r="D10" s="38" t="n"/>
-      <c r="E10" s="38" t="n"/>
-      <c r="F10" s="38" t="n"/>
-      <c r="G10" s="38" t="n"/>
-      <c r="H10" s="38" t="n"/>
-      <c r="I10" s="38" t="n"/>
-      <c r="J10" s="47" t="n"/>
-    </row>
-    <row r="11" ht="21" customHeight="1" s="70">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="B10" s="98" t="n"/>
+      <c r="C10" s="98" t="n"/>
+      <c r="D10" s="98" t="n"/>
+      <c r="E10" s="98" t="n"/>
+      <c r="F10" s="98" t="n"/>
+      <c r="G10" s="98" t="n"/>
+      <c r="H10" s="98" t="n"/>
+      <c r="I10" s="98" t="n"/>
+      <c r="J10" s="98" t="n"/>
+      <c r="K10" s="97" t="n"/>
+    </row>
+    <row r="11" ht="21" customHeight="1" s="127">
+      <c r="A11" s="59" t="inlineStr">
         <is>
           <t>Proyecto / Obra</t>
         </is>
       </c>
-      <c r="B11" s="31" t="n"/>
-      <c r="C11" s="50" t="n"/>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="30" t="n"/>
-      <c r="F11" s="30" t="n"/>
-      <c r="G11" s="31" t="n"/>
-      <c r="H11" s="33" t="inlineStr">
+      <c r="B11" s="89" t="n"/>
+      <c r="C11" s="161" t="n"/>
+      <c r="D11" s="93" t="n"/>
+      <c r="E11" s="93" t="n"/>
+      <c r="F11" s="93" t="n"/>
+      <c r="G11" s="89" t="n"/>
+      <c r="H11" s="59" t="inlineStr">
         <is>
           <t>Contratista / Empresa</t>
         </is>
       </c>
-      <c r="I11" s="43" t="n"/>
-      <c r="J11" s="31" t="n"/>
-    </row>
-    <row r="12" ht="21" customHeight="1" s="70">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="I11" s="353" t="n"/>
+      <c r="J11" s="93" t="n"/>
+      <c r="K11" s="89" t="n"/>
+    </row>
+    <row r="12" ht="21" customHeight="1" s="127">
+      <c r="A12" s="59" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="B12" s="31" t="n"/>
-      <c r="C12" s="43" t="n"/>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="30" t="n"/>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="31" t="n"/>
-      <c r="H12" s="33" t="inlineStr">
+      <c r="B12" s="89" t="n"/>
+      <c r="C12" s="68" t="n"/>
+      <c r="D12" s="93" t="n"/>
+      <c r="E12" s="93" t="n"/>
+      <c r="F12" s="93" t="n"/>
+      <c r="G12" s="89" t="n"/>
+      <c r="H12" s="59" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="I12" s="48" t="n"/>
-      <c r="J12" s="31" t="n"/>
-    </row>
-    <row r="13" ht="21" customHeight="1" s="70">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="I12" s="353" t="n"/>
+      <c r="J12" s="93" t="n"/>
+      <c r="K12" s="89" t="n"/>
+    </row>
+    <row r="13" ht="21" customHeight="1" s="127">
+      <c r="A13" s="59" t="inlineStr">
         <is>
           <t>Tarea o actividad a analizar</t>
         </is>
       </c>
-      <c r="B13" s="31" t="n"/>
-      <c r="C13" s="43" t="n"/>
-      <c r="D13" s="30" t="n"/>
-      <c r="E13" s="30" t="n"/>
-      <c r="F13" s="30" t="n"/>
-      <c r="G13" s="30" t="n"/>
-      <c r="H13" s="30" t="n"/>
-      <c r="I13" s="30" t="n"/>
-      <c r="J13" s="31" t="n"/>
-    </row>
-    <row r="14" ht="21" customHeight="1" s="70">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="B13" s="89" t="n"/>
+      <c r="C13" s="68" t="n"/>
+      <c r="D13" s="93" t="n"/>
+      <c r="E13" s="93" t="n"/>
+      <c r="F13" s="93" t="n"/>
+      <c r="G13" s="93" t="n"/>
+      <c r="H13" s="93" t="n"/>
+      <c r="I13" s="93" t="n"/>
+      <c r="J13" s="93" t="n"/>
+      <c r="K13" s="89" t="n"/>
+    </row>
+    <row r="14" ht="21" customHeight="1" s="127">
+      <c r="A14" s="59" t="inlineStr">
         <is>
           <t>Área / frente de trabajo</t>
         </is>
       </c>
-      <c r="B14" s="31" t="n"/>
-      <c r="C14" s="43" t="n"/>
-      <c r="D14" s="31" t="n"/>
-      <c r="E14" s="33" t="inlineStr">
+      <c r="B14" s="89" t="n"/>
+      <c r="C14" s="68" t="n"/>
+      <c r="D14" s="89" t="n"/>
+      <c r="E14" s="59" t="inlineStr">
         <is>
           <t>N° de ATS</t>
         </is>
       </c>
-      <c r="F14" s="30" t="n"/>
-      <c r="G14" s="31" t="n"/>
-      <c r="H14" s="48" t="n"/>
-      <c r="I14" s="33" t="inlineStr">
+      <c r="F14" s="93" t="n"/>
+      <c r="G14" s="89" t="n"/>
+      <c r="H14" s="69" t="n"/>
+      <c r="I14" s="59" t="inlineStr">
         <is>
           <t>Hora inicio</t>
         </is>
       </c>
-      <c r="J14" s="48" t="n"/>
-    </row>
-    <row r="15" ht="21" customHeight="1" s="70">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="J14" s="120" t="n"/>
+      <c r="K14" s="89" t="n"/>
+    </row>
+    <row r="15" ht="21" customHeight="1" s="127">
+      <c r="A15" s="59" t="inlineStr">
         <is>
           <t>Supervisor responsable</t>
         </is>
       </c>
-      <c r="B15" s="31" t="n"/>
-      <c r="C15" s="43" t="n"/>
-      <c r="D15" s="31" t="n"/>
-      <c r="E15" s="33" t="inlineStr">
+      <c r="B15" s="89" t="n"/>
+      <c r="C15" s="68" t="n"/>
+      <c r="D15" s="89" t="n"/>
+      <c r="E15" s="59" t="inlineStr">
         <is>
           <t>Cargo del supervisor</t>
         </is>
       </c>
-      <c r="F15" s="30" t="n"/>
-      <c r="G15" s="31" t="n"/>
-      <c r="H15" s="43" t="n"/>
-      <c r="I15" s="33" t="inlineStr">
+      <c r="F15" s="93" t="n"/>
+      <c r="G15" s="89" t="n"/>
+      <c r="H15" s="68" t="n"/>
+      <c r="I15" s="59" t="inlineStr">
         <is>
           <t>Hora fin</t>
         </is>
       </c>
-      <c r="J15" s="48" t="n"/>
-    </row>
-    <row r="16" ht="21" customHeight="1" s="70">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="J15" s="120" t="n"/>
+      <c r="K15" s="89" t="n"/>
+    </row>
+    <row r="16" ht="21" customHeight="1" s="127">
+      <c r="A16" s="59" t="inlineStr">
         <is>
           <t>Permiso de trabajo asociado (N°)</t>
         </is>
       </c>
-      <c r="B16" s="31" t="n"/>
-      <c r="C16" s="43" t="n"/>
-      <c r="D16" s="30" t="n"/>
-      <c r="E16" s="30" t="n"/>
-      <c r="F16" s="30" t="n"/>
-      <c r="G16" s="30" t="n"/>
-      <c r="H16" s="30" t="n"/>
-      <c r="I16" s="30" t="n"/>
-      <c r="J16" s="31" t="n"/>
-    </row>
-    <row r="17" ht="16.5" customHeight="1" s="70">
-      <c r="A17" s="54" t="inlineStr">
+      <c r="B16" s="89" t="n"/>
+      <c r="C16" s="68" t="n"/>
+      <c r="D16" s="93" t="n"/>
+      <c r="E16" s="93" t="n"/>
+      <c r="F16" s="93" t="n"/>
+      <c r="G16" s="93" t="n"/>
+      <c r="H16" s="93" t="n"/>
+      <c r="I16" s="93" t="n"/>
+      <c r="J16" s="93" t="n"/>
+      <c r="K16" s="89" t="n"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" s="127">
+      <c r="A17" s="227" t="inlineStr">
         <is>
           <t>2. ANÁLISIS DE LA TAREA</t>
         </is>
       </c>
-      <c r="B17" s="38" t="n"/>
-      <c r="C17" s="38" t="n"/>
-      <c r="D17" s="38" t="n"/>
-      <c r="E17" s="38" t="n"/>
-      <c r="F17" s="38" t="n"/>
-      <c r="G17" s="38" t="n"/>
-      <c r="H17" s="38" t="n"/>
-      <c r="I17" s="38" t="n"/>
-      <c r="J17" s="47" t="n"/>
-    </row>
-    <row r="18" ht="25.95" customHeight="1" s="70">
-      <c r="A18" s="103" t="inlineStr">
+      <c r="K17" s="92" t="n"/>
+    </row>
+    <row r="18" ht="25.95" customHeight="1" s="127">
+      <c r="A18" s="255" t="inlineStr">
         <is>
           <t>Probabilidad: 1 baja · 2 media · 3 alta   |   Severidad: 1 leve · 2 grave · 3 mortal o incapacitante   |   Nivel = Probabilidad × Severidad: 1-2 Bajo · 3-4 Medio · 6-9 Alto   |   Controles: eliminación, sustitución, ingeniería, administrativos, EPP</t>
         </is>
       </c>
-      <c r="B18" s="115" t="n"/>
-      <c r="C18" s="115" t="n"/>
-      <c r="D18" s="115" t="n"/>
-      <c r="E18" s="115" t="n"/>
-      <c r="F18" s="115" t="n"/>
-      <c r="G18" s="115" t="n"/>
-      <c r="H18" s="115" t="n"/>
-      <c r="I18" s="115" t="n"/>
-      <c r="J18" s="116" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1" s="70">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="B18" s="349" t="n"/>
+      <c r="C18" s="349" t="n"/>
+      <c r="D18" s="349" t="n"/>
+      <c r="E18" s="349" t="n"/>
+      <c r="F18" s="349" t="n"/>
+      <c r="G18" s="349" t="n"/>
+      <c r="H18" s="349" t="n"/>
+      <c r="I18" s="349" t="n"/>
+      <c r="J18" s="349" t="n"/>
+      <c r="K18" s="351" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="127">
+      <c r="A19" s="296" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B19" s="34" t="inlineStr">
+      <c r="B19" s="296" t="inlineStr">
         <is>
           <t>Paso de la tarea</t>
         </is>
       </c>
-      <c r="C19" s="34" t="inlineStr">
+      <c r="C19" s="296" t="inlineStr">
         <is>
           <t>Peligro identificado</t>
         </is>
       </c>
-      <c r="D19" s="34" t="inlineStr">
+      <c r="D19" s="296" t="inlineStr">
         <is>
           <t>Riesgo / consecuencia</t>
         </is>
       </c>
-      <c r="E19" s="34" t="inlineStr">
+      <c r="E19" s="296" t="inlineStr">
         <is>
           <t>Prob. (1-3)</t>
         </is>
       </c>
-      <c r="F19" s="34" t="inlineStr">
+      <c r="F19" s="296" t="inlineStr">
         <is>
           <t>Sev. (1-3)</t>
         </is>
       </c>
-      <c r="G19" s="34" t="inlineStr">
+      <c r="G19" s="296" t="inlineStr">
         <is>
           <t>Nivel</t>
         </is>
       </c>
-      <c r="H19" s="34" t="inlineStr">
+      <c r="H19" s="296" t="inlineStr">
         <is>
           <t>Medidas de control</t>
         </is>
       </c>
-      <c r="I19" s="34" t="inlineStr">
+      <c r="I19" s="97" t="n"/>
+      <c r="J19" s="296" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="J19" s="34" t="inlineStr">
+      <c r="K19" s="296" t="inlineStr">
         <is>
           <t>Nivel residual</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="28.05" customHeight="1" s="70">
-      <c r="A20" s="57" t="n">
+    <row r="20" ht="28.05" customHeight="1" s="127">
+      <c r="A20" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="89" t="n"/>
-      <c r="C20" s="89" t="n"/>
-      <c r="D20" s="89" t="n"/>
-      <c r="E20" s="57" t="n"/>
-      <c r="F20" s="57" t="n"/>
-      <c r="G20" s="57">
+      <c r="B20" s="72" t="n"/>
+      <c r="C20" s="72" t="n"/>
+      <c r="D20" s="72" t="n"/>
+      <c r="E20" s="126" t="n"/>
+      <c r="F20" s="126" t="n"/>
+      <c r="G20" s="126">
         <f>IF(OR(E20="",F20=""),"",IF(E20*F20&gt;=6,"Alto",IF(E20*F20&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H20" s="89" t="n"/>
+      <c r="H20" s="72" t="n"/>
       <c r="I20" s="89" t="n"/>
-      <c r="J20" s="57" t="n"/>
-    </row>
-    <row r="21" ht="28.05" customHeight="1" s="70">
-      <c r="A21" s="57" t="n">
+      <c r="J20" s="72" t="n"/>
+      <c r="K20" s="126" t="n"/>
+    </row>
+    <row r="21" ht="28.05" customHeight="1" s="127">
+      <c r="A21" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="89" t="n"/>
-      <c r="C21" s="89" t="n"/>
-      <c r="D21" s="89" t="n"/>
-      <c r="E21" s="57" t="n"/>
-      <c r="F21" s="57" t="n"/>
-      <c r="G21" s="57">
+      <c r="B21" s="72" t="n"/>
+      <c r="C21" s="72" t="n"/>
+      <c r="D21" s="72" t="n"/>
+      <c r="E21" s="126" t="n"/>
+      <c r="F21" s="126" t="n"/>
+      <c r="G21" s="126">
         <f>IF(OR(E21="",F21=""),"",IF(E21*F21&gt;=6,"Alto",IF(E21*F21&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H21" s="89" t="n"/>
+      <c r="H21" s="72" t="n"/>
       <c r="I21" s="89" t="n"/>
-      <c r="J21" s="57" t="n"/>
-    </row>
-    <row r="22" ht="28.05" customHeight="1" s="70">
-      <c r="A22" s="57" t="n">
+      <c r="J21" s="72" t="n"/>
+      <c r="K21" s="126" t="n"/>
+    </row>
+    <row r="22" ht="28.05" customHeight="1" s="127">
+      <c r="A22" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="89" t="n"/>
-      <c r="C22" s="89" t="n"/>
-      <c r="D22" s="89" t="n"/>
-      <c r="E22" s="57" t="n"/>
-      <c r="F22" s="57" t="n"/>
-      <c r="G22" s="57">
+      <c r="B22" s="72" t="n"/>
+      <c r="C22" s="72" t="n"/>
+      <c r="D22" s="72" t="n"/>
+      <c r="E22" s="126" t="n"/>
+      <c r="F22" s="126" t="n"/>
+      <c r="G22" s="126">
         <f>IF(OR(E22="",F22=""),"",IF(E22*F22&gt;=6,"Alto",IF(E22*F22&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H22" s="89" t="n"/>
+      <c r="H22" s="72" t="n"/>
       <c r="I22" s="89" t="n"/>
-      <c r="J22" s="57" t="n"/>
-    </row>
-    <row r="23" ht="28.05" customHeight="1" s="70">
-      <c r="A23" s="57" t="n">
+      <c r="J22" s="72" t="n"/>
+      <c r="K22" s="126" t="n"/>
+    </row>
+    <row r="23" ht="28.05" customHeight="1" s="127">
+      <c r="A23" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="89" t="n"/>
-      <c r="C23" s="89" t="n"/>
-      <c r="D23" s="89" t="n"/>
-      <c r="E23" s="57" t="n"/>
-      <c r="F23" s="57" t="n"/>
-      <c r="G23" s="57">
+      <c r="B23" s="72" t="n"/>
+      <c r="C23" s="72" t="n"/>
+      <c r="D23" s="72" t="n"/>
+      <c r="E23" s="126" t="n"/>
+      <c r="F23" s="126" t="n"/>
+      <c r="G23" s="126">
         <f>IF(OR(E23="",F23=""),"",IF(E23*F23&gt;=6,"Alto",IF(E23*F23&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H23" s="89" t="n"/>
+      <c r="H23" s="72" t="n"/>
       <c r="I23" s="89" t="n"/>
-      <c r="J23" s="57" t="n"/>
-    </row>
-    <row r="24" ht="28.05" customHeight="1" s="70">
-      <c r="A24" s="57" t="n">
+      <c r="J23" s="72" t="n"/>
+      <c r="K23" s="126" t="n"/>
+    </row>
+    <row r="24" ht="28.05" customHeight="1" s="127">
+      <c r="A24" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="89" t="n"/>
-      <c r="C24" s="89" t="n"/>
-      <c r="D24" s="89" t="n"/>
-      <c r="E24" s="57" t="n"/>
-      <c r="F24" s="57" t="n"/>
-      <c r="G24" s="57">
+      <c r="B24" s="72" t="n"/>
+      <c r="C24" s="72" t="n"/>
+      <c r="D24" s="72" t="n"/>
+      <c r="E24" s="126" t="n"/>
+      <c r="F24" s="126" t="n"/>
+      <c r="G24" s="126">
         <f>IF(OR(E24="",F24=""),"",IF(E24*F24&gt;=6,"Alto",IF(E24*F24&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H24" s="89" t="n"/>
+      <c r="H24" s="72" t="n"/>
       <c r="I24" s="89" t="n"/>
-      <c r="J24" s="57" t="n"/>
-    </row>
-    <row r="25" ht="28.05" customHeight="1" s="70">
-      <c r="A25" s="57" t="n">
+      <c r="J24" s="72" t="n"/>
+      <c r="K24" s="126" t="n"/>
+    </row>
+    <row r="25" ht="28.05" customHeight="1" s="127">
+      <c r="A25" s="126" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="89" t="n"/>
-      <c r="C25" s="89" t="n"/>
-      <c r="D25" s="89" t="n"/>
-      <c r="E25" s="57" t="n"/>
-      <c r="F25" s="57" t="n"/>
-      <c r="G25" s="57">
+      <c r="B25" s="72" t="n"/>
+      <c r="C25" s="72" t="n"/>
+      <c r="D25" s="72" t="n"/>
+      <c r="E25" s="126" t="n"/>
+      <c r="F25" s="126" t="n"/>
+      <c r="G25" s="126">
         <f>IF(OR(E25="",F25=""),"",IF(E25*F25&gt;=6,"Alto",IF(E25*F25&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H25" s="89" t="n"/>
+      <c r="H25" s="72" t="n"/>
       <c r="I25" s="89" t="n"/>
-      <c r="J25" s="57" t="n"/>
-    </row>
-    <row r="26" ht="28.05" customHeight="1" s="70">
-      <c r="A26" s="57" t="n">
+      <c r="J25" s="72" t="n"/>
+      <c r="K25" s="126" t="n"/>
+    </row>
+    <row r="26" ht="28.05" customHeight="1" s="127">
+      <c r="A26" s="126" t="n">
         <v>7</v>
       </c>
-      <c r="B26" s="89" t="n"/>
-      <c r="C26" s="89" t="n"/>
-      <c r="D26" s="89" t="n"/>
-      <c r="E26" s="57" t="n"/>
-      <c r="F26" s="57" t="n"/>
-      <c r="G26" s="57">
+      <c r="B26" s="72" t="n"/>
+      <c r="C26" s="72" t="n"/>
+      <c r="D26" s="72" t="n"/>
+      <c r="E26" s="126" t="n"/>
+      <c r="F26" s="126" t="n"/>
+      <c r="G26" s="126">
         <f>IF(OR(E26="",F26=""),"",IF(E26*F26&gt;=6,"Alto",IF(E26*F26&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H26" s="89" t="n"/>
+      <c r="H26" s="72" t="n"/>
       <c r="I26" s="89" t="n"/>
-      <c r="J26" s="57" t="n"/>
-    </row>
-    <row r="27" ht="28.05" customHeight="1" s="70">
-      <c r="A27" s="57" t="n">
+      <c r="J26" s="72" t="n"/>
+      <c r="K26" s="126" t="n"/>
+    </row>
+    <row r="27" ht="28.05" customHeight="1" s="127">
+      <c r="A27" s="126" t="n">
         <v>8</v>
       </c>
-      <c r="B27" s="89" t="n"/>
-      <c r="C27" s="89" t="n"/>
-      <c r="D27" s="89" t="n"/>
-      <c r="E27" s="57" t="n"/>
-      <c r="F27" s="57" t="n"/>
-      <c r="G27" s="57">
+      <c r="B27" s="72" t="n"/>
+      <c r="C27" s="72" t="n"/>
+      <c r="D27" s="72" t="n"/>
+      <c r="E27" s="126" t="n"/>
+      <c r="F27" s="126" t="n"/>
+      <c r="G27" s="126">
         <f>IF(OR(E27="",F27=""),"",IF(E27*F27&gt;=6,"Alto",IF(E27*F27&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H27" s="89" t="n"/>
+      <c r="H27" s="72" t="n"/>
       <c r="I27" s="89" t="n"/>
-      <c r="J27" s="57" t="n"/>
-    </row>
-    <row r="28" ht="28.05" customHeight="1" s="70">
-      <c r="A28" s="57" t="n">
+      <c r="J27" s="72" t="n"/>
+      <c r="K27" s="126" t="n"/>
+    </row>
+    <row r="28" ht="28.05" customHeight="1" s="127">
+      <c r="A28" s="126" t="n">
         <v>9</v>
       </c>
-      <c r="B28" s="89" t="n"/>
-      <c r="C28" s="89" t="n"/>
-      <c r="D28" s="89" t="n"/>
-      <c r="E28" s="57" t="n"/>
-      <c r="F28" s="57" t="n"/>
-      <c r="G28" s="57">
+      <c r="B28" s="72" t="n"/>
+      <c r="C28" s="72" t="n"/>
+      <c r="D28" s="72" t="n"/>
+      <c r="E28" s="126" t="n"/>
+      <c r="F28" s="126" t="n"/>
+      <c r="G28" s="126">
         <f>IF(OR(E28="",F28=""),"",IF(E28*F28&gt;=6,"Alto",IF(E28*F28&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H28" s="89" t="n"/>
+      <c r="H28" s="72" t="n"/>
       <c r="I28" s="89" t="n"/>
-      <c r="J28" s="57" t="n"/>
-    </row>
-    <row r="29" ht="28.05" customHeight="1" s="70">
-      <c r="A29" s="57" t="n">
+      <c r="J28" s="72" t="n"/>
+      <c r="K28" s="126" t="n"/>
+    </row>
+    <row r="29" ht="28.05" customHeight="1" s="127">
+      <c r="A29" s="126" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="89" t="n"/>
-      <c r="C29" s="89" t="n"/>
-      <c r="D29" s="89" t="n"/>
-      <c r="E29" s="57" t="n"/>
-      <c r="F29" s="57" t="n"/>
-      <c r="G29" s="57">
+      <c r="B29" s="72" t="n"/>
+      <c r="C29" s="72" t="n"/>
+      <c r="D29" s="72" t="n"/>
+      <c r="E29" s="126" t="n"/>
+      <c r="F29" s="126" t="n"/>
+      <c r="G29" s="126">
         <f>IF(OR(E29="",F29=""),"",IF(E29*F29&gt;=6,"Alto",IF(E29*F29&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H29" s="89" t="n"/>
+      <c r="H29" s="72" t="n"/>
       <c r="I29" s="89" t="n"/>
-      <c r="J29" s="57" t="n"/>
-    </row>
-    <row r="30" ht="28.05" customHeight="1" s="70">
-      <c r="A30" s="57" t="n">
+      <c r="J29" s="72" t="n"/>
+      <c r="K29" s="126" t="n"/>
+    </row>
+    <row r="30" ht="28.05" customHeight="1" s="127">
+      <c r="A30" s="126" t="n">
         <v>11</v>
       </c>
-      <c r="B30" s="89" t="n"/>
-      <c r="C30" s="89" t="n"/>
-      <c r="D30" s="89" t="n"/>
-      <c r="E30" s="57" t="n"/>
-      <c r="F30" s="57" t="n"/>
-      <c r="G30" s="57">
+      <c r="B30" s="72" t="n"/>
+      <c r="C30" s="72" t="n"/>
+      <c r="D30" s="72" t="n"/>
+      <c r="E30" s="126" t="n"/>
+      <c r="F30" s="126" t="n"/>
+      <c r="G30" s="126">
         <f>IF(OR(E30="",F30=""),"",IF(E30*F30&gt;=6,"Alto",IF(E30*F30&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H30" s="89" t="n"/>
+      <c r="H30" s="72" t="n"/>
       <c r="I30" s="89" t="n"/>
-      <c r="J30" s="57" t="n"/>
-    </row>
-    <row r="31" ht="28.05" customHeight="1" s="70">
-      <c r="A31" s="57" t="n">
+      <c r="J30" s="72" t="n"/>
+      <c r="K30" s="126" t="n"/>
+    </row>
+    <row r="31" ht="28.05" customHeight="1" s="127">
+      <c r="A31" s="126" t="n">
         <v>12</v>
       </c>
-      <c r="B31" s="89" t="n"/>
-      <c r="C31" s="89" t="n"/>
-      <c r="D31" s="89" t="n"/>
-      <c r="E31" s="57" t="n"/>
-      <c r="F31" s="57" t="n"/>
-      <c r="G31" s="57">
+      <c r="B31" s="72" t="n"/>
+      <c r="C31" s="72" t="n"/>
+      <c r="D31" s="72" t="n"/>
+      <c r="E31" s="126" t="n"/>
+      <c r="F31" s="126" t="n"/>
+      <c r="G31" s="126">
         <f>IF(OR(E31="",F31=""),"",IF(E31*F31&gt;=6,"Alto",IF(E31*F31&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H31" s="89" t="n"/>
+      <c r="H31" s="72" t="n"/>
       <c r="I31" s="89" t="n"/>
-      <c r="J31" s="57" t="n"/>
-    </row>
-    <row r="32" ht="16.5" customHeight="1" s="70">
-      <c r="A32" s="54" t="inlineStr">
+      <c r="J31" s="72" t="n"/>
+      <c r="K31" s="126" t="n"/>
+    </row>
+    <row r="32" ht="16.5" customHeight="1" s="127">
+      <c r="A32" s="227" t="inlineStr">
         <is>
           <t>3. EPP Y PERMISOS REQUERIDOS</t>
         </is>
       </c>
-      <c r="B32" s="38" t="n"/>
-      <c r="C32" s="38" t="n"/>
-      <c r="D32" s="38" t="n"/>
-      <c r="E32" s="38" t="n"/>
-      <c r="F32" s="38" t="n"/>
-      <c r="G32" s="38" t="n"/>
-      <c r="H32" s="38" t="n"/>
-      <c r="I32" s="38" t="n"/>
-      <c r="J32" s="47" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="70">
-      <c r="A33" s="88" t="inlineStr">
+      <c r="K32" s="92" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="127">
+      <c r="A33" s="247" t="inlineStr">
         <is>
           <t>EPP requerido para esta tarea (marque los que apliquen)</t>
         </is>
       </c>
-      <c r="B33" s="30" t="n"/>
-      <c r="C33" s="30" t="n"/>
-      <c r="D33" s="30" t="n"/>
-      <c r="E33" s="30" t="n"/>
-      <c r="F33" s="30" t="n"/>
-      <c r="G33" s="30" t="n"/>
-      <c r="H33" s="30" t="n"/>
-      <c r="I33" s="30" t="n"/>
-      <c r="J33" s="31" t="n"/>
-    </row>
-    <row r="34" ht="18" customHeight="1" s="70">
-      <c r="A34" s="89" t="inlineStr">
+      <c r="B33" s="349" t="n"/>
+      <c r="C33" s="349" t="n"/>
+      <c r="D33" s="349" t="n"/>
+      <c r="E33" s="349" t="n"/>
+      <c r="F33" s="349" t="n"/>
+      <c r="G33" s="349" t="n"/>
+      <c r="H33" s="349" t="n"/>
+      <c r="I33" s="349" t="n"/>
+      <c r="J33" s="349" t="n"/>
+      <c r="K33" s="350" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1" s="127">
+      <c r="A34" s="230" t="inlineStr">
         <is>
           <t>☐ Casco de seguridad</t>
         </is>
       </c>
-      <c r="B34" s="30" t="n"/>
-      <c r="C34" s="31" t="n"/>
-      <c r="D34" s="89" t="inlineStr">
+      <c r="B34" s="98" t="n"/>
+      <c r="C34" s="97" t="n"/>
+      <c r="D34" s="230" t="inlineStr">
         <is>
           <t>☐ Gafas de seguridad</t>
         </is>
       </c>
-      <c r="E34" s="30" t="n"/>
-      <c r="F34" s="31" t="n"/>
-      <c r="G34" s="89" t="inlineStr">
+      <c r="E34" s="98" t="n"/>
+      <c r="F34" s="97" t="n"/>
+      <c r="G34" s="230" t="inlineStr">
         <is>
           <t>☐ Guantes de seguridad</t>
         </is>
       </c>
-      <c r="H34" s="31" t="n"/>
-      <c r="I34" s="89" t="inlineStr">
+      <c r="H34" s="97" t="n"/>
+      <c r="I34" s="230" t="inlineStr">
         <is>
           <t>☐ Botas de seguridad</t>
         </is>
       </c>
-      <c r="J34" s="31" t="n"/>
-    </row>
-    <row r="35" ht="18" customHeight="1" s="70">
-      <c r="A35" s="89" t="inlineStr">
+      <c r="J34" s="98" t="n"/>
+      <c r="K34" s="97" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1" s="127">
+      <c r="A35" s="72" t="inlineStr">
         <is>
           <t>☐ Arnés y línea de vida</t>
         </is>
       </c>
-      <c r="B35" s="30" t="n"/>
-      <c r="C35" s="31" t="n"/>
-      <c r="D35" s="89" t="inlineStr">
+      <c r="B35" s="93" t="n"/>
+      <c r="C35" s="89" t="n"/>
+      <c r="D35" s="72" t="inlineStr">
         <is>
           <t>☐ Protección auditiva</t>
         </is>
       </c>
-      <c r="E35" s="30" t="n"/>
-      <c r="F35" s="31" t="n"/>
-      <c r="G35" s="89" t="inlineStr">
+      <c r="E35" s="93" t="n"/>
+      <c r="F35" s="89" t="n"/>
+      <c r="G35" s="72" t="inlineStr">
         <is>
           <t>☐ Respirador / mascarilla</t>
         </is>
       </c>
-      <c r="H35" s="31" t="n"/>
-      <c r="I35" s="89" t="inlineStr">
+      <c r="H35" s="89" t="n"/>
+      <c r="I35" s="72" t="inlineStr">
         <is>
           <t>☐ Chaleco reflectivo</t>
         </is>
       </c>
-      <c r="J35" s="31" t="n"/>
-    </row>
-    <row r="36" ht="18" customHeight="1" s="70">
-      <c r="A36" s="89" t="inlineStr">
+      <c r="J35" s="93" t="n"/>
+      <c r="K35" s="89" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1" s="127">
+      <c r="A36" s="72" t="inlineStr">
         <is>
           <t>☐ Careta o protector facial</t>
         </is>
       </c>
-      <c r="B36" s="30" t="n"/>
-      <c r="C36" s="31" t="n"/>
-      <c r="D36" s="89" t="inlineStr">
+      <c r="B36" s="93" t="n"/>
+      <c r="C36" s="89" t="n"/>
+      <c r="D36" s="72" t="inlineStr">
         <is>
           <t>☐ Overol / ropa de trabajo</t>
         </is>
       </c>
-      <c r="E36" s="30" t="n"/>
-      <c r="F36" s="31" t="n"/>
-      <c r="G36" s="89" t="inlineStr">
+      <c r="E36" s="93" t="n"/>
+      <c r="F36" s="89" t="n"/>
+      <c r="G36" s="72" t="inlineStr">
         <is>
           <t>☐ Impermeable</t>
         </is>
       </c>
-      <c r="H36" s="31" t="n"/>
-      <c r="I36" s="89" t="inlineStr">
+      <c r="H36" s="89" t="n"/>
+      <c r="I36" s="72" t="inlineStr">
         <is>
           <t>☐ Otro: ____________</t>
         </is>
       </c>
-      <c r="J36" s="31" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="70">
-      <c r="A37" s="88" t="inlineStr">
+      <c r="J36" s="93" t="n"/>
+      <c r="K36" s="89" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="127">
+      <c r="A37" s="159" t="inlineStr">
         <is>
           <t>Permisos y requisitos asociados (marque los que apliquen)</t>
         </is>
       </c>
-      <c r="B37" s="30" t="n"/>
-      <c r="C37" s="30" t="n"/>
-      <c r="D37" s="30" t="n"/>
-      <c r="E37" s="30" t="n"/>
-      <c r="F37" s="30" t="n"/>
-      <c r="G37" s="30" t="n"/>
-      <c r="H37" s="30" t="n"/>
-      <c r="I37" s="30" t="n"/>
-      <c r="J37" s="31" t="n"/>
-    </row>
-    <row r="38" ht="18" customHeight="1" s="70">
-      <c r="A38" s="89" t="inlineStr">
+      <c r="B37" s="93" t="n"/>
+      <c r="C37" s="93" t="n"/>
+      <c r="D37" s="93" t="n"/>
+      <c r="E37" s="93" t="n"/>
+      <c r="F37" s="93" t="n"/>
+      <c r="G37" s="93" t="n"/>
+      <c r="H37" s="93" t="n"/>
+      <c r="I37" s="93" t="n"/>
+      <c r="J37" s="93" t="n"/>
+      <c r="K37" s="89" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" s="127">
+      <c r="A38" s="72" t="inlineStr">
         <is>
           <t>☐ Permiso de alturas</t>
         </is>
       </c>
-      <c r="B38" s="30" t="n"/>
-      <c r="C38" s="31" t="n"/>
-      <c r="D38" s="89" t="inlineStr">
+      <c r="B38" s="93" t="n"/>
+      <c r="C38" s="89" t="n"/>
+      <c r="D38" s="72" t="inlineStr">
         <is>
           <t>☐ Permiso en caliente</t>
         </is>
       </c>
-      <c r="E38" s="30" t="n"/>
-      <c r="F38" s="31" t="n"/>
-      <c r="G38" s="89" t="inlineStr">
+      <c r="E38" s="93" t="n"/>
+      <c r="F38" s="89" t="n"/>
+      <c r="G38" s="72" t="inlineStr">
         <is>
           <t>☐ Espacios confinados</t>
         </is>
       </c>
-      <c r="H38" s="31" t="n"/>
-      <c r="I38" s="89" t="inlineStr">
+      <c r="H38" s="89" t="n"/>
+      <c r="I38" s="72" t="inlineStr">
         <is>
           <t>☐ Excavaciones</t>
         </is>
       </c>
-      <c r="J38" s="31" t="n"/>
-    </row>
-    <row r="39" ht="18" customHeight="1" s="70">
-      <c r="A39" s="89" t="inlineStr">
+      <c r="J38" s="93" t="n"/>
+      <c r="K38" s="89" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1" s="127">
+      <c r="A39" s="72" t="inlineStr">
         <is>
           <t>☐ Bloqueo y etiquetado (LOTO)</t>
         </is>
       </c>
-      <c r="B39" s="30" t="n"/>
-      <c r="C39" s="31" t="n"/>
-      <c r="D39" s="89" t="inlineStr">
+      <c r="B39" s="93" t="n"/>
+      <c r="C39" s="89" t="n"/>
+      <c r="D39" s="72" t="inlineStr">
         <is>
           <t>☐ Plan de izaje</t>
         </is>
       </c>
-      <c r="E39" s="30" t="n"/>
-      <c r="F39" s="31" t="n"/>
-      <c r="G39" s="89" t="inlineStr">
+      <c r="E39" s="93" t="n"/>
+      <c r="F39" s="89" t="n"/>
+      <c r="G39" s="72" t="inlineStr">
         <is>
           <t>☐ Ninguno</t>
         </is>
       </c>
-      <c r="H39" s="31" t="n"/>
-      <c r="I39" s="89" t="inlineStr">
+      <c r="H39" s="89" t="n"/>
+      <c r="I39" s="72" t="inlineStr">
         <is>
           <t>☐ Otro: ____________</t>
         </is>
       </c>
-      <c r="J39" s="31" t="n"/>
-    </row>
-    <row r="40" ht="16.5" customHeight="1" s="70">
-      <c r="A40" s="54" t="inlineStr">
+      <c r="J39" s="93" t="n"/>
+      <c r="K39" s="89" t="n"/>
+    </row>
+    <row r="40" ht="16.5" customHeight="1" s="127">
+      <c r="A40" s="227" t="inlineStr">
         <is>
           <t>4. EQUIPO DE TRABAJO Y SOCIALIZACIÓN</t>
         </is>
       </c>
-      <c r="B40" s="38" t="n"/>
-      <c r="C40" s="38" t="n"/>
-      <c r="D40" s="38" t="n"/>
-      <c r="E40" s="38" t="n"/>
-      <c r="F40" s="38" t="n"/>
-      <c r="G40" s="38" t="n"/>
-      <c r="H40" s="38" t="n"/>
-      <c r="I40" s="38" t="n"/>
-      <c r="J40" s="47" t="n"/>
-    </row>
-    <row r="41" ht="19.95" customHeight="1" s="70">
-      <c r="A41" s="43" t="inlineStr">
+      <c r="K40" s="92" t="n"/>
+    </row>
+    <row r="41" ht="19.95" customHeight="1" s="127">
+      <c r="A41" s="298" t="inlineStr">
         <is>
           <t>Con mi firma confirmo que participé en este ATS, entendí los peligros y los controles, y me comprometo a aplicarlos durante el trabajo.</t>
         </is>
       </c>
-      <c r="B41" s="30" t="n"/>
-      <c r="C41" s="30" t="n"/>
-      <c r="D41" s="30" t="n"/>
-      <c r="E41" s="30" t="n"/>
-      <c r="F41" s="30" t="n"/>
-      <c r="G41" s="30" t="n"/>
-      <c r="H41" s="30" t="n"/>
-      <c r="I41" s="30" t="n"/>
-      <c r="J41" s="31" t="n"/>
-    </row>
-    <row r="42" ht="19.05" customHeight="1" s="70">
-      <c r="A42" s="34" t="inlineStr">
+      <c r="B41" s="349" t="n"/>
+      <c r="C41" s="349" t="n"/>
+      <c r="D41" s="349" t="n"/>
+      <c r="E41" s="349" t="n"/>
+      <c r="F41" s="349" t="n"/>
+      <c r="G41" s="349" t="n"/>
+      <c r="H41" s="349" t="n"/>
+      <c r="I41" s="349" t="n"/>
+      <c r="J41" s="349" t="n"/>
+      <c r="K41" s="350" t="n"/>
+    </row>
+    <row r="42" ht="19.05" customHeight="1" s="127">
+      <c r="A42" s="296" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B42" s="34" t="inlineStr">
+      <c r="B42" s="296" t="inlineStr">
         <is>
           <t>Nombre completo</t>
         </is>
       </c>
-      <c r="C42" s="34" t="inlineStr">
+      <c r="C42" s="296" t="inlineStr">
         <is>
           <t>Documento</t>
         </is>
       </c>
-      <c r="D42" s="34" t="inlineStr">
+      <c r="D42" s="296" t="inlineStr">
         <is>
           <t>Cargo / oficio</t>
         </is>
       </c>
-      <c r="E42" s="34" t="inlineStr">
+      <c r="E42" s="296" t="inlineStr">
         <is>
           <t>Firma</t>
         </is>
       </c>
-      <c r="F42" s="30" t="n"/>
-      <c r="G42" s="30" t="n"/>
-      <c r="H42" s="31" t="n"/>
-      <c r="I42" s="34" t="inlineStr">
+      <c r="F42" s="98" t="n"/>
+      <c r="G42" s="98" t="n"/>
+      <c r="H42" s="97" t="n"/>
+      <c r="I42" s="296" t="inlineStr">
         <is>
           <t>Hora de socialización</t>
         </is>
       </c>
-      <c r="J42" s="31" t="n"/>
-    </row>
-    <row r="43" ht="19.05" customHeight="1" s="70">
-      <c r="A43" s="57" t="n">
+      <c r="J42" s="98" t="n"/>
+      <c r="K42" s="97" t="n"/>
+    </row>
+    <row r="43" ht="19.05" customHeight="1" s="127">
+      <c r="A43" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="B43" s="29" t="n"/>
-      <c r="C43" s="29" t="n"/>
-      <c r="D43" s="29" t="n"/>
-      <c r="E43" s="29" t="n"/>
-      <c r="F43" s="30" t="n"/>
-      <c r="G43" s="30" t="n"/>
-      <c r="H43" s="31" t="n"/>
-      <c r="I43" s="29" t="n"/>
-      <c r="J43" s="31" t="n"/>
-    </row>
-    <row r="44" ht="19.05" customHeight="1" s="70">
-      <c r="A44" s="57" t="n">
+      <c r="B43" s="76" t="n"/>
+      <c r="C43" s="76" t="n"/>
+      <c r="D43" s="76" t="n"/>
+      <c r="E43" s="76" t="n"/>
+      <c r="F43" s="93" t="n"/>
+      <c r="G43" s="93" t="n"/>
+      <c r="H43" s="89" t="n"/>
+      <c r="I43" s="120" t="n"/>
+      <c r="J43" s="93" t="n"/>
+      <c r="K43" s="89" t="n"/>
+    </row>
+    <row r="44" ht="19.05" customHeight="1" s="127">
+      <c r="A44" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="B44" s="29" t="n"/>
-      <c r="C44" s="29" t="n"/>
-      <c r="D44" s="29" t="n"/>
-      <c r="E44" s="29" t="n"/>
-      <c r="F44" s="30" t="n"/>
-      <c r="G44" s="30" t="n"/>
-      <c r="H44" s="31" t="n"/>
-      <c r="I44" s="29" t="n"/>
-      <c r="J44" s="31" t="n"/>
-    </row>
-    <row r="45" ht="19.05" customHeight="1" s="70">
-      <c r="A45" s="57" t="n">
+      <c r="B44" s="76" t="n"/>
+      <c r="C44" s="76" t="n"/>
+      <c r="D44" s="76" t="n"/>
+      <c r="E44" s="76" t="n"/>
+      <c r="F44" s="93" t="n"/>
+      <c r="G44" s="93" t="n"/>
+      <c r="H44" s="89" t="n"/>
+      <c r="I44" s="120" t="n"/>
+      <c r="J44" s="93" t="n"/>
+      <c r="K44" s="89" t="n"/>
+    </row>
+    <row r="45" ht="19.05" customHeight="1" s="127">
+      <c r="A45" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="B45" s="29" t="n"/>
-      <c r="C45" s="29" t="n"/>
-      <c r="D45" s="29" t="n"/>
-      <c r="E45" s="29" t="n"/>
-      <c r="F45" s="30" t="n"/>
-      <c r="G45" s="30" t="n"/>
-      <c r="H45" s="31" t="n"/>
-      <c r="I45" s="29" t="n"/>
-      <c r="J45" s="31" t="n"/>
-    </row>
-    <row r="46" ht="19.05" customHeight="1" s="70">
-      <c r="A46" s="57" t="n">
+      <c r="B45" s="76" t="n"/>
+      <c r="C45" s="76" t="n"/>
+      <c r="D45" s="76" t="n"/>
+      <c r="E45" s="76" t="n"/>
+      <c r="F45" s="93" t="n"/>
+      <c r="G45" s="93" t="n"/>
+      <c r="H45" s="89" t="n"/>
+      <c r="I45" s="120" t="n"/>
+      <c r="J45" s="93" t="n"/>
+      <c r="K45" s="89" t="n"/>
+    </row>
+    <row r="46" ht="19.05" customHeight="1" s="127">
+      <c r="A46" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="B46" s="29" t="n"/>
-      <c r="C46" s="29" t="n"/>
-      <c r="D46" s="29" t="n"/>
-      <c r="E46" s="29" t="n"/>
-      <c r="F46" s="30" t="n"/>
-      <c r="G46" s="30" t="n"/>
-      <c r="H46" s="31" t="n"/>
-      <c r="I46" s="29" t="n"/>
-      <c r="J46" s="31" t="n"/>
-    </row>
-    <row r="47" ht="19.05" customHeight="1" s="70">
-      <c r="A47" s="57" t="n">
+      <c r="B46" s="76" t="n"/>
+      <c r="C46" s="76" t="n"/>
+      <c r="D46" s="76" t="n"/>
+      <c r="E46" s="76" t="n"/>
+      <c r="F46" s="93" t="n"/>
+      <c r="G46" s="93" t="n"/>
+      <c r="H46" s="89" t="n"/>
+      <c r="I46" s="120" t="n"/>
+      <c r="J46" s="93" t="n"/>
+      <c r="K46" s="89" t="n"/>
+    </row>
+    <row r="47" ht="19.05" customHeight="1" s="127">
+      <c r="A47" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="B47" s="29" t="n"/>
-      <c r="C47" s="29" t="n"/>
-      <c r="D47" s="29" t="n"/>
-      <c r="E47" s="29" t="n"/>
-      <c r="F47" s="30" t="n"/>
-      <c r="G47" s="30" t="n"/>
-      <c r="H47" s="31" t="n"/>
-      <c r="I47" s="29" t="n"/>
-      <c r="J47" s="31" t="n"/>
-    </row>
-    <row r="48" ht="19.05" customHeight="1" s="70">
-      <c r="A48" s="57" t="n">
+      <c r="B47" s="76" t="n"/>
+      <c r="C47" s="76" t="n"/>
+      <c r="D47" s="76" t="n"/>
+      <c r="E47" s="76" t="n"/>
+      <c r="F47" s="93" t="n"/>
+      <c r="G47" s="93" t="n"/>
+      <c r="H47" s="89" t="n"/>
+      <c r="I47" s="120" t="n"/>
+      <c r="J47" s="93" t="n"/>
+      <c r="K47" s="89" t="n"/>
+    </row>
+    <row r="48" ht="19.05" customHeight="1" s="127">
+      <c r="A48" s="126" t="n">
         <v>6</v>
       </c>
-      <c r="B48" s="29" t="n"/>
-      <c r="C48" s="29" t="n"/>
-      <c r="D48" s="29" t="n"/>
-      <c r="E48" s="29" t="n"/>
-      <c r="F48" s="30" t="n"/>
-      <c r="G48" s="30" t="n"/>
-      <c r="H48" s="31" t="n"/>
-      <c r="I48" s="29" t="n"/>
-      <c r="J48" s="31" t="n"/>
-    </row>
-    <row r="49" ht="19.05" customHeight="1" s="70">
-      <c r="A49" s="57" t="n">
+      <c r="B48" s="76" t="n"/>
+      <c r="C48" s="76" t="n"/>
+      <c r="D48" s="76" t="n"/>
+      <c r="E48" s="76" t="n"/>
+      <c r="F48" s="93" t="n"/>
+      <c r="G48" s="93" t="n"/>
+      <c r="H48" s="89" t="n"/>
+      <c r="I48" s="120" t="n"/>
+      <c r="J48" s="93" t="n"/>
+      <c r="K48" s="89" t="n"/>
+    </row>
+    <row r="49" ht="19.05" customHeight="1" s="127">
+      <c r="A49" s="126" t="n">
         <v>7</v>
       </c>
-      <c r="B49" s="29" t="n"/>
-      <c r="C49" s="29" t="n"/>
-      <c r="D49" s="29" t="n"/>
-      <c r="E49" s="29" t="n"/>
-      <c r="F49" s="30" t="n"/>
-      <c r="G49" s="30" t="n"/>
-      <c r="H49" s="31" t="n"/>
-      <c r="I49" s="29" t="n"/>
-      <c r="J49" s="31" t="n"/>
-    </row>
-    <row r="50" ht="19.05" customHeight="1" s="70">
-      <c r="A50" s="57" t="n">
+      <c r="B49" s="76" t="n"/>
+      <c r="C49" s="76" t="n"/>
+      <c r="D49" s="76" t="n"/>
+      <c r="E49" s="76" t="n"/>
+      <c r="F49" s="93" t="n"/>
+      <c r="G49" s="93" t="n"/>
+      <c r="H49" s="89" t="n"/>
+      <c r="I49" s="120" t="n"/>
+      <c r="J49" s="93" t="n"/>
+      <c r="K49" s="89" t="n"/>
+    </row>
+    <row r="50" ht="19.05" customHeight="1" s="127">
+      <c r="A50" s="126" t="n">
         <v>8</v>
       </c>
-      <c r="B50" s="29" t="n"/>
-      <c r="C50" s="29" t="n"/>
-      <c r="D50" s="29" t="n"/>
-      <c r="E50" s="29" t="n"/>
-      <c r="F50" s="30" t="n"/>
-      <c r="G50" s="30" t="n"/>
-      <c r="H50" s="31" t="n"/>
-      <c r="I50" s="29" t="n"/>
-      <c r="J50" s="31" t="n"/>
-    </row>
-    <row r="51" ht="16.5" customHeight="1" s="70">
-      <c r="A51" s="54" t="inlineStr">
+      <c r="B50" s="76" t="n"/>
+      <c r="C50" s="76" t="n"/>
+      <c r="D50" s="76" t="n"/>
+      <c r="E50" s="76" t="n"/>
+      <c r="F50" s="93" t="n"/>
+      <c r="G50" s="93" t="n"/>
+      <c r="H50" s="89" t="n"/>
+      <c r="I50" s="120" t="n"/>
+      <c r="J50" s="93" t="n"/>
+      <c r="K50" s="89" t="n"/>
+    </row>
+    <row r="51" ht="16.5" customHeight="1" s="127">
+      <c r="A51" s="137" t="inlineStr">
         <is>
           <t>5. PLAN DE EMERGENCIA PARA ESTA TAREA</t>
         </is>
       </c>
-      <c r="B51" s="38" t="n"/>
-      <c r="C51" s="38" t="n"/>
-      <c r="D51" s="38" t="n"/>
-      <c r="E51" s="38" t="n"/>
-      <c r="F51" s="38" t="n"/>
-      <c r="G51" s="38" t="n"/>
-      <c r="H51" s="38" t="n"/>
-      <c r="I51" s="38" t="n"/>
-      <c r="J51" s="47" t="n"/>
-    </row>
-    <row r="52" ht="21" customHeight="1" s="70">
-      <c r="A52" s="33" t="inlineStr">
+      <c r="B51" s="98" t="n"/>
+      <c r="C51" s="98" t="n"/>
+      <c r="D51" s="98" t="n"/>
+      <c r="E51" s="98" t="n"/>
+      <c r="F51" s="98" t="n"/>
+      <c r="G51" s="98" t="n"/>
+      <c r="H51" s="98" t="n"/>
+      <c r="I51" s="98" t="n"/>
+      <c r="J51" s="98" t="n"/>
+      <c r="K51" s="97" t="n"/>
+    </row>
+    <row r="52" ht="21" customHeight="1" s="127">
+      <c r="A52" s="59" t="inlineStr">
         <is>
           <t>Punto de encuentro</t>
         </is>
       </c>
-      <c r="B52" s="31" t="n"/>
-      <c r="C52" s="43" t="n"/>
-      <c r="D52" s="31" t="n"/>
-      <c r="E52" s="33" t="inlineStr">
+      <c r="B52" s="89" t="n"/>
+      <c r="C52" s="68" t="n"/>
+      <c r="D52" s="89" t="n"/>
+      <c r="E52" s="59" t="inlineStr">
         <is>
           <t>Teléfono de emergencias</t>
         </is>
       </c>
-      <c r="F52" s="30" t="n"/>
-      <c r="G52" s="31" t="n"/>
-      <c r="H52" s="43" t="n"/>
-      <c r="I52" s="33" t="inlineStr">
+      <c r="F52" s="93" t="n"/>
+      <c r="G52" s="89" t="n"/>
+      <c r="H52" s="68" t="n"/>
+      <c r="I52" s="59" t="inlineStr">
         <is>
           <t>Brigadista</t>
         </is>
       </c>
-      <c r="J52" s="43" t="n"/>
-    </row>
-    <row r="53" ht="21" customHeight="1" s="70">
-      <c r="A53" s="33" t="inlineStr">
+      <c r="J52" s="124" t="n"/>
+      <c r="K52" s="89" t="n"/>
+    </row>
+    <row r="53" ht="21" customHeight="1" s="127">
+      <c r="A53" s="59" t="inlineStr">
         <is>
           <t>Centro de salud más cercano</t>
         </is>
       </c>
-      <c r="B53" s="31" t="n"/>
-      <c r="C53" s="43" t="n"/>
-      <c r="D53" s="31" t="n"/>
-      <c r="E53" s="33" t="inlineStr">
+      <c r="B53" s="89" t="n"/>
+      <c r="C53" s="68" t="n"/>
+      <c r="D53" s="89" t="n"/>
+      <c r="E53" s="59" t="inlineStr">
         <is>
           <t>Ruta de evacuación o rescate</t>
         </is>
       </c>
-      <c r="F53" s="30" t="n"/>
-      <c r="G53" s="31" t="n"/>
-      <c r="H53" s="43" t="n"/>
-      <c r="I53" s="30" t="n"/>
-      <c r="J53" s="31" t="n"/>
-    </row>
-    <row r="54" ht="16.5" customHeight="1" s="70">
-      <c r="A54" s="54" t="inlineStr">
+      <c r="F53" s="93" t="n"/>
+      <c r="G53" s="89" t="n"/>
+      <c r="H53" s="68" t="n"/>
+      <c r="I53" s="93" t="n"/>
+      <c r="J53" s="93" t="n"/>
+      <c r="K53" s="89" t="n"/>
+    </row>
+    <row r="54" ht="16.5" customHeight="1" s="127">
+      <c r="A54" s="227" t="inlineStr">
         <is>
           <t>6. FIRMAS</t>
         </is>
       </c>
-      <c r="B54" s="38" t="n"/>
-      <c r="C54" s="38" t="n"/>
-      <c r="D54" s="38" t="n"/>
-      <c r="E54" s="38" t="n"/>
-      <c r="F54" s="38" t="n"/>
-      <c r="G54" s="38" t="n"/>
-      <c r="H54" s="38" t="n"/>
-      <c r="I54" s="38" t="n"/>
-      <c r="J54" s="47" t="n"/>
-    </row>
-    <row r="55" ht="18" customHeight="1" s="70">
-      <c r="A55" s="51" t="inlineStr">
+      <c r="K54" s="92" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1" s="127">
+      <c r="A55" s="261" t="inlineStr">
         <is>
           <t>ELABORÓ — SUPERVISOR DE LA TAREA</t>
         </is>
       </c>
-      <c r="B55" s="30" t="n"/>
-      <c r="C55" s="31" t="n"/>
-      <c r="D55" s="51" t="inlineStr">
+      <c r="B55" s="347" t="n"/>
+      <c r="C55" s="348" t="n"/>
+      <c r="D55" s="261" t="inlineStr">
         <is>
           <t>REVISÓ — RESPONSABLE SST</t>
         </is>
       </c>
-      <c r="E55" s="30" t="n"/>
-      <c r="F55" s="30" t="n"/>
-      <c r="G55" s="31" t="n"/>
-      <c r="H55" s="51" t="inlineStr">
+      <c r="E55" s="347" t="n"/>
+      <c r="F55" s="347" t="n"/>
+      <c r="G55" s="348" t="n"/>
+      <c r="H55" s="261" t="inlineStr">
         <is>
           <t>APROBÓ — RESIDENTE / DIRECTOR DE OBRA</t>
         </is>
       </c>
-      <c r="I55" s="30" t="n"/>
-      <c r="J55" s="31" t="n"/>
-    </row>
-    <row r="56" ht="42" customHeight="1" s="70">
-      <c r="A56" s="39" t="inlineStr">
+      <c r="I55" s="347" t="n"/>
+      <c r="J55" s="347" t="n"/>
+      <c r="K55" s="348" t="n"/>
+    </row>
+    <row r="56" ht="42" customHeight="1" s="127">
+      <c r="A56" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="B56" s="31" t="n"/>
-      <c r="C56" s="43" t="n"/>
-      <c r="D56" s="39" t="inlineStr">
+      <c r="B56" s="97" t="n"/>
+      <c r="C56" s="301" t="n"/>
+      <c r="D56" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="E56" s="31" t="n"/>
-      <c r="F56" s="43" t="n"/>
-      <c r="G56" s="31" t="n"/>
-      <c r="H56" s="39" t="inlineStr">
+      <c r="E56" s="97" t="n"/>
+      <c r="F56" s="301" t="n"/>
+      <c r="G56" s="97" t="n"/>
+      <c r="H56" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="I56" s="43" t="n"/>
-      <c r="J56" s="31" t="n"/>
-    </row>
-    <row r="57" ht="21" customHeight="1" s="70">
-      <c r="A57" s="39" t="inlineStr">
+      <c r="I56" s="354" t="n"/>
+      <c r="J56" s="98" t="n"/>
+      <c r="K56" s="97" t="n"/>
+    </row>
+    <row r="57" ht="21" customHeight="1" s="127">
+      <c r="A57" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="B57" s="31" t="n"/>
-      <c r="C57" s="43" t="n"/>
-      <c r="D57" s="39" t="inlineStr">
+      <c r="B57" s="89" t="n"/>
+      <c r="C57" s="68" t="n"/>
+      <c r="D57" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="E57" s="31" t="n"/>
-      <c r="F57" s="43" t="n"/>
-      <c r="G57" s="31" t="n"/>
-      <c r="H57" s="39" t="inlineStr">
+      <c r="E57" s="89" t="n"/>
+      <c r="F57" s="68" t="n"/>
+      <c r="G57" s="89" t="n"/>
+      <c r="H57" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="I57" s="43" t="n"/>
-      <c r="J57" s="31" t="n"/>
-    </row>
-    <row r="58" ht="21" customHeight="1" s="70">
-      <c r="A58" s="39" t="inlineStr">
+      <c r="I57" s="355" t="n"/>
+      <c r="J57" s="93" t="n"/>
+      <c r="K57" s="89" t="n"/>
+    </row>
+    <row r="58" ht="21" customHeight="1" s="127">
+      <c r="A58" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="B58" s="31" t="n"/>
-      <c r="C58" s="43" t="n"/>
-      <c r="D58" s="39" t="inlineStr">
+      <c r="B58" s="89" t="n"/>
+      <c r="C58" s="68" t="n"/>
+      <c r="D58" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="43" t="n"/>
-      <c r="G58" s="31" t="n"/>
-      <c r="H58" s="39" t="inlineStr">
+      <c r="E58" s="89" t="n"/>
+      <c r="F58" s="68" t="n"/>
+      <c r="G58" s="89" t="n"/>
+      <c r="H58" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="I58" s="43" t="n"/>
-      <c r="J58" s="31" t="n"/>
+      <c r="I58" s="355" t="n"/>
+      <c r="J58" s="93" t="n"/>
+      <c r="K58" s="89" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="61" t="inlineStr">
+      <c r="A59" s="25" t="inlineStr">
         <is>
           <t>REV. 04/10/2026</t>
         </is>
       </c>
-      <c r="F59" s="63">
-        <f>I5</f>
+      <c r="F59" s="105">
+        <f>J5</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="97">
+  <mergeCells count="116">
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A51:K51"/>
+    <mergeCell ref="I56:K56"/>
     <mergeCell ref="D55:G55"/>
     <mergeCell ref="E15:G15"/>
     <mergeCell ref="E47:H47"/>
+    <mergeCell ref="A54:K54"/>
+    <mergeCell ref="H53:K53"/>
+    <mergeCell ref="A41:K41"/>
     <mergeCell ref="D39:F39"/>
     <mergeCell ref="A56:B56"/>
-    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="H55:K55"/>
     <mergeCell ref="G34:H34"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="I34:K34"/>
     <mergeCell ref="D56:E56"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="F56:G56"/>
+    <mergeCell ref="A17:K17"/>
     <mergeCell ref="A53:B53"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="C13:J13"/>
+    <mergeCell ref="I49:K49"/>
+    <mergeCell ref="D3:K3"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="H23:I23"/>
     <mergeCell ref="E49:H49"/>
     <mergeCell ref="F57:G57"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="F59:K59"/>
+    <mergeCell ref="I47:K47"/>
     <mergeCell ref="E45:H45"/>
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I46:J46"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="I12:K12"/>
     <mergeCell ref="A55:C55"/>
-    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="H25:I25"/>
     <mergeCell ref="G38:H38"/>
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="C16:J16"/>
-    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="I4:K4"/>
     <mergeCell ref="A38:C38"/>
-    <mergeCell ref="I43:J43"/>
     <mergeCell ref="E48:H48"/>
     <mergeCell ref="C12:G12"/>
-    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="D1:K2"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H28:I28"/>
     <mergeCell ref="G35:H35"/>
-    <mergeCell ref="I35:J35"/>
     <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="A10:K10"/>
     <mergeCell ref="C53:D53"/>
-    <mergeCell ref="D3:J3"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="H31:I31"/>
     <mergeCell ref="G39:H39"/>
-    <mergeCell ref="F59:J59"/>
-    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="H21:I21"/>
     <mergeCell ref="E50:H50"/>
-    <mergeCell ref="A51:J51"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="A37:K37"/>
     <mergeCell ref="A12:B12"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="D7:H7"/>
     <mergeCell ref="A57:B57"/>
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="D35:F35"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A54:J54"/>
-    <mergeCell ref="H53:J53"/>
-    <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="H22:I22"/>
     <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D8:H8"/>
     <mergeCell ref="E14:G14"/>
-    <mergeCell ref="H55:J55"/>
     <mergeCell ref="D36:F36"/>
     <mergeCell ref="E46:H46"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="A33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="C16:K16"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="J14:K14"/>
     <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="I58:K58"/>
     <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="J6:K6"/>
     <mergeCell ref="D57:E57"/>
     <mergeCell ref="E43:H43"/>
-    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="I35:K35"/>
     <mergeCell ref="A35:C35"/>
+    <mergeCell ref="I44:K44"/>
     <mergeCell ref="E42:H42"/>
     <mergeCell ref="D38:F38"/>
-    <mergeCell ref="I12:J12"/>
     <mergeCell ref="E53:G53"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="C13:K13"/>
     <mergeCell ref="E44:H44"/>
-    <mergeCell ref="I5:J5"/>
     <mergeCell ref="C52:D52"/>
     <mergeCell ref="D58:E58"/>
     <mergeCell ref="A39:C39"/>
-    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="D4:H4"/>
     <mergeCell ref="F58:G58"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="I46:K46"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="E52:G52"/>
-    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="H24:I24"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D1:J2"/>
+    <mergeCell ref="J8:K8"/>
     <mergeCell ref="A58:B58"/>
+    <mergeCell ref="H26:I26"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.7" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>

--- a/public/plantilla-ats.xlsx
+++ b/public/plantilla-ats.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATS" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,7 +15,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="39">
+  <numFmts count="0"/>
+  <fonts count="40">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -296,6 +297,10 @@
       <color rgb="FF0B1F33"/>
       <sz val="9"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="20">
@@ -1024,7 +1029,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="374">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -1928,6 +1933,55 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2440,7 +2494,10 @@
     <col width="5" customWidth="1" style="127" min="1" max="1"/>
     <col width="28" customWidth="1" style="127" min="2" max="2"/>
     <col width="24" customWidth="1" style="127" min="3" max="4"/>
+    <col width="13" customWidth="1" style="127" min="4" max="4"/>
     <col width="10.77734375" customWidth="1" style="127" min="5" max="7"/>
+    <col width="13" customWidth="1" style="127" min="6" max="6"/>
+    <col width="13" customWidth="1" style="127" min="7" max="7"/>
     <col width="40" customWidth="1" style="127" min="8" max="8"/>
     <col width="15.77734375" customWidth="1" style="127" min="9" max="9"/>
     <col width="15.77734375" customWidth="1" style="127" min="10" max="10"/>
@@ -2593,19 +2650,19 @@
         </is>
       </c>
       <c r="B11" s="89" t="n"/>
-      <c r="C11" s="161" t="n"/>
-      <c r="D11" s="93" t="n"/>
-      <c r="E11" s="93" t="n"/>
-      <c r="F11" s="93" t="n"/>
-      <c r="G11" s="89" t="n"/>
+      <c r="C11" s="360" t="n"/>
+      <c r="D11" s="361" t="n"/>
+      <c r="E11" s="361" t="n"/>
+      <c r="F11" s="361" t="n"/>
+      <c r="G11" s="362" t="n"/>
       <c r="H11" s="59" t="inlineStr">
         <is>
           <t>Contratista / Empresa</t>
         </is>
       </c>
-      <c r="I11" s="353" t="n"/>
-      <c r="J11" s="93" t="n"/>
-      <c r="K11" s="89" t="n"/>
+      <c r="I11" s="363" t="n"/>
+      <c r="J11" s="361" t="n"/>
+      <c r="K11" s="362" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="127">
       <c r="A12" s="59" t="inlineStr">
@@ -2614,19 +2671,19 @@
         </is>
       </c>
       <c r="B12" s="89" t="n"/>
-      <c r="C12" s="68" t="n"/>
-      <c r="D12" s="93" t="n"/>
-      <c r="E12" s="93" t="n"/>
-      <c r="F12" s="93" t="n"/>
-      <c r="G12" s="89" t="n"/>
+      <c r="C12" s="364" t="n"/>
+      <c r="D12" s="361" t="n"/>
+      <c r="E12" s="361" t="n"/>
+      <c r="F12" s="361" t="n"/>
+      <c r="G12" s="362" t="n"/>
       <c r="H12" s="59" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="I12" s="353" t="n"/>
-      <c r="J12" s="93" t="n"/>
-      <c r="K12" s="89" t="n"/>
+      <c r="I12" s="363" t="n"/>
+      <c r="J12" s="361" t="n"/>
+      <c r="K12" s="362" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="127">
       <c r="A13" s="59" t="inlineStr">
@@ -2635,15 +2692,15 @@
         </is>
       </c>
       <c r="B13" s="89" t="n"/>
-      <c r="C13" s="68" t="n"/>
-      <c r="D13" s="93" t="n"/>
-      <c r="E13" s="93" t="n"/>
-      <c r="F13" s="93" t="n"/>
-      <c r="G13" s="93" t="n"/>
-      <c r="H13" s="93" t="n"/>
-      <c r="I13" s="93" t="n"/>
-      <c r="J13" s="93" t="n"/>
-      <c r="K13" s="89" t="n"/>
+      <c r="C13" s="364" t="n"/>
+      <c r="D13" s="361" t="n"/>
+      <c r="E13" s="361" t="n"/>
+      <c r="F13" s="361" t="n"/>
+      <c r="G13" s="361" t="n"/>
+      <c r="H13" s="361" t="n"/>
+      <c r="I13" s="361" t="n"/>
+      <c r="J13" s="361" t="n"/>
+      <c r="K13" s="362" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="127">
       <c r="A14" s="59" t="inlineStr">
@@ -2652,8 +2709,8 @@
         </is>
       </c>
       <c r="B14" s="89" t="n"/>
-      <c r="C14" s="68" t="n"/>
-      <c r="D14" s="89" t="n"/>
+      <c r="C14" s="364" t="n"/>
+      <c r="D14" s="362" t="n"/>
       <c r="E14" s="59" t="inlineStr">
         <is>
           <t>N° de ATS</t>
@@ -2661,7 +2718,7 @@
       </c>
       <c r="F14" s="93" t="n"/>
       <c r="G14" s="89" t="n"/>
-      <c r="H14" s="69" t="n"/>
+      <c r="H14" s="365" t="n"/>
       <c r="I14" s="59" t="inlineStr">
         <is>
           <t>Hora inicio</t>
@@ -2677,8 +2734,8 @@
         </is>
       </c>
       <c r="B15" s="89" t="n"/>
-      <c r="C15" s="68" t="n"/>
-      <c r="D15" s="89" t="n"/>
+      <c r="C15" s="364" t="n"/>
+      <c r="D15" s="362" t="n"/>
       <c r="E15" s="59" t="inlineStr">
         <is>
           <t>Cargo del supervisor</t>
@@ -2686,7 +2743,7 @@
       </c>
       <c r="F15" s="93" t="n"/>
       <c r="G15" s="89" t="n"/>
-      <c r="H15" s="68" t="n"/>
+      <c r="H15" s="364" t="n"/>
       <c r="I15" s="59" t="inlineStr">
         <is>
           <t>Hora fin</t>
@@ -2702,15 +2759,15 @@
         </is>
       </c>
       <c r="B16" s="89" t="n"/>
-      <c r="C16" s="68" t="n"/>
-      <c r="D16" s="93" t="n"/>
-      <c r="E16" s="93" t="n"/>
-      <c r="F16" s="93" t="n"/>
-      <c r="G16" s="93" t="n"/>
-      <c r="H16" s="93" t="n"/>
-      <c r="I16" s="93" t="n"/>
-      <c r="J16" s="93" t="n"/>
-      <c r="K16" s="89" t="n"/>
+      <c r="C16" s="364" t="n"/>
+      <c r="D16" s="361" t="n"/>
+      <c r="E16" s="361" t="n"/>
+      <c r="F16" s="361" t="n"/>
+      <c r="G16" s="361" t="n"/>
+      <c r="H16" s="361" t="n"/>
+      <c r="I16" s="361" t="n"/>
+      <c r="J16" s="361" t="n"/>
+      <c r="K16" s="362" t="n"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="127">
       <c r="A17" s="227" t="inlineStr">
@@ -2791,220 +2848,220 @@
       </c>
     </row>
     <row r="20" ht="28.05" customHeight="1" s="127">
-      <c r="A20" s="126" t="n">
+      <c r="A20" s="366" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="72" t="n"/>
-      <c r="C20" s="72" t="n"/>
-      <c r="D20" s="72" t="n"/>
-      <c r="E20" s="126" t="n"/>
-      <c r="F20" s="126" t="n"/>
-      <c r="G20" s="126">
+      <c r="B20" s="364" t="n"/>
+      <c r="C20" s="364" t="n"/>
+      <c r="D20" s="364" t="n"/>
+      <c r="E20" s="367" t="n"/>
+      <c r="F20" s="367" t="n"/>
+      <c r="G20" s="366">
         <f>IF(OR(E20="",F20=""),"",IF(E20*F20&gt;=6,"Alto",IF(E20*F20&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H20" s="72" t="n"/>
-      <c r="I20" s="89" t="n"/>
-      <c r="J20" s="72" t="n"/>
-      <c r="K20" s="126" t="n"/>
+      <c r="H20" s="364" t="n"/>
+      <c r="I20" s="362" t="n"/>
+      <c r="J20" s="364" t="n"/>
+      <c r="K20" s="367" t="n"/>
     </row>
     <row r="21" ht="28.05" customHeight="1" s="127">
-      <c r="A21" s="126" t="n">
+      <c r="A21" s="366" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="72" t="n"/>
-      <c r="C21" s="72" t="n"/>
-      <c r="D21" s="72" t="n"/>
-      <c r="E21" s="126" t="n"/>
-      <c r="F21" s="126" t="n"/>
-      <c r="G21" s="126">
+      <c r="B21" s="364" t="n"/>
+      <c r="C21" s="364" t="n"/>
+      <c r="D21" s="364" t="n"/>
+      <c r="E21" s="367" t="n"/>
+      <c r="F21" s="367" t="n"/>
+      <c r="G21" s="366">
         <f>IF(OR(E21="",F21=""),"",IF(E21*F21&gt;=6,"Alto",IF(E21*F21&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H21" s="72" t="n"/>
-      <c r="I21" s="89" t="n"/>
-      <c r="J21" s="72" t="n"/>
-      <c r="K21" s="126" t="n"/>
+      <c r="H21" s="364" t="n"/>
+      <c r="I21" s="362" t="n"/>
+      <c r="J21" s="364" t="n"/>
+      <c r="K21" s="367" t="n"/>
     </row>
     <row r="22" ht="28.05" customHeight="1" s="127">
-      <c r="A22" s="126" t="n">
+      <c r="A22" s="366" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="72" t="n"/>
-      <c r="C22" s="72" t="n"/>
-      <c r="D22" s="72" t="n"/>
-      <c r="E22" s="126" t="n"/>
-      <c r="F22" s="126" t="n"/>
-      <c r="G22" s="126">
+      <c r="B22" s="364" t="n"/>
+      <c r="C22" s="364" t="n"/>
+      <c r="D22" s="364" t="n"/>
+      <c r="E22" s="367" t="n"/>
+      <c r="F22" s="367" t="n"/>
+      <c r="G22" s="366">
         <f>IF(OR(E22="",F22=""),"",IF(E22*F22&gt;=6,"Alto",IF(E22*F22&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H22" s="72" t="n"/>
-      <c r="I22" s="89" t="n"/>
-      <c r="J22" s="72" t="n"/>
-      <c r="K22" s="126" t="n"/>
+      <c r="H22" s="364" t="n"/>
+      <c r="I22" s="362" t="n"/>
+      <c r="J22" s="364" t="n"/>
+      <c r="K22" s="367" t="n"/>
     </row>
     <row r="23" ht="28.05" customHeight="1" s="127">
-      <c r="A23" s="126" t="n">
+      <c r="A23" s="366" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="72" t="n"/>
-      <c r="C23" s="72" t="n"/>
-      <c r="D23" s="72" t="n"/>
-      <c r="E23" s="126" t="n"/>
-      <c r="F23" s="126" t="n"/>
-      <c r="G23" s="126">
+      <c r="B23" s="364" t="n"/>
+      <c r="C23" s="364" t="n"/>
+      <c r="D23" s="364" t="n"/>
+      <c r="E23" s="367" t="n"/>
+      <c r="F23" s="367" t="n"/>
+      <c r="G23" s="366">
         <f>IF(OR(E23="",F23=""),"",IF(E23*F23&gt;=6,"Alto",IF(E23*F23&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H23" s="72" t="n"/>
-      <c r="I23" s="89" t="n"/>
-      <c r="J23" s="72" t="n"/>
-      <c r="K23" s="126" t="n"/>
+      <c r="H23" s="364" t="n"/>
+      <c r="I23" s="362" t="n"/>
+      <c r="J23" s="364" t="n"/>
+      <c r="K23" s="367" t="n"/>
     </row>
     <row r="24" ht="28.05" customHeight="1" s="127">
-      <c r="A24" s="126" t="n">
+      <c r="A24" s="366" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="72" t="n"/>
-      <c r="C24" s="72" t="n"/>
-      <c r="D24" s="72" t="n"/>
-      <c r="E24" s="126" t="n"/>
-      <c r="F24" s="126" t="n"/>
-      <c r="G24" s="126">
+      <c r="B24" s="364" t="n"/>
+      <c r="C24" s="364" t="n"/>
+      <c r="D24" s="364" t="n"/>
+      <c r="E24" s="367" t="n"/>
+      <c r="F24" s="367" t="n"/>
+      <c r="G24" s="366">
         <f>IF(OR(E24="",F24=""),"",IF(E24*F24&gt;=6,"Alto",IF(E24*F24&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H24" s="72" t="n"/>
-      <c r="I24" s="89" t="n"/>
-      <c r="J24" s="72" t="n"/>
-      <c r="K24" s="126" t="n"/>
+      <c r="H24" s="364" t="n"/>
+      <c r="I24" s="362" t="n"/>
+      <c r="J24" s="364" t="n"/>
+      <c r="K24" s="367" t="n"/>
     </row>
     <row r="25" ht="28.05" customHeight="1" s="127">
-      <c r="A25" s="126" t="n">
+      <c r="A25" s="366" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="72" t="n"/>
-      <c r="C25" s="72" t="n"/>
-      <c r="D25" s="72" t="n"/>
-      <c r="E25" s="126" t="n"/>
-      <c r="F25" s="126" t="n"/>
-      <c r="G25" s="126">
+      <c r="B25" s="364" t="n"/>
+      <c r="C25" s="364" t="n"/>
+      <c r="D25" s="364" t="n"/>
+      <c r="E25" s="367" t="n"/>
+      <c r="F25" s="367" t="n"/>
+      <c r="G25" s="366">
         <f>IF(OR(E25="",F25=""),"",IF(E25*F25&gt;=6,"Alto",IF(E25*F25&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H25" s="72" t="n"/>
-      <c r="I25" s="89" t="n"/>
-      <c r="J25" s="72" t="n"/>
-      <c r="K25" s="126" t="n"/>
+      <c r="H25" s="364" t="n"/>
+      <c r="I25" s="362" t="n"/>
+      <c r="J25" s="364" t="n"/>
+      <c r="K25" s="367" t="n"/>
     </row>
     <row r="26" ht="28.05" customHeight="1" s="127">
-      <c r="A26" s="126" t="n">
+      <c r="A26" s="366" t="n">
         <v>7</v>
       </c>
-      <c r="B26" s="72" t="n"/>
-      <c r="C26" s="72" t="n"/>
-      <c r="D26" s="72" t="n"/>
-      <c r="E26" s="126" t="n"/>
-      <c r="F26" s="126" t="n"/>
-      <c r="G26" s="126">
+      <c r="B26" s="364" t="n"/>
+      <c r="C26" s="364" t="n"/>
+      <c r="D26" s="364" t="n"/>
+      <c r="E26" s="367" t="n"/>
+      <c r="F26" s="367" t="n"/>
+      <c r="G26" s="366">
         <f>IF(OR(E26="",F26=""),"",IF(E26*F26&gt;=6,"Alto",IF(E26*F26&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H26" s="72" t="n"/>
-      <c r="I26" s="89" t="n"/>
-      <c r="J26" s="72" t="n"/>
-      <c r="K26" s="126" t="n"/>
+      <c r="H26" s="364" t="n"/>
+      <c r="I26" s="362" t="n"/>
+      <c r="J26" s="364" t="n"/>
+      <c r="K26" s="367" t="n"/>
     </row>
     <row r="27" ht="28.05" customHeight="1" s="127">
-      <c r="A27" s="126" t="n">
+      <c r="A27" s="366" t="n">
         <v>8</v>
       </c>
-      <c r="B27" s="72" t="n"/>
-      <c r="C27" s="72" t="n"/>
-      <c r="D27" s="72" t="n"/>
-      <c r="E27" s="126" t="n"/>
-      <c r="F27" s="126" t="n"/>
-      <c r="G27" s="126">
+      <c r="B27" s="364" t="n"/>
+      <c r="C27" s="364" t="n"/>
+      <c r="D27" s="364" t="n"/>
+      <c r="E27" s="367" t="n"/>
+      <c r="F27" s="367" t="n"/>
+      <c r="G27" s="366">
         <f>IF(OR(E27="",F27=""),"",IF(E27*F27&gt;=6,"Alto",IF(E27*F27&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H27" s="72" t="n"/>
-      <c r="I27" s="89" t="n"/>
-      <c r="J27" s="72" t="n"/>
-      <c r="K27" s="126" t="n"/>
+      <c r="H27" s="364" t="n"/>
+      <c r="I27" s="362" t="n"/>
+      <c r="J27" s="364" t="n"/>
+      <c r="K27" s="367" t="n"/>
     </row>
     <row r="28" ht="28.05" customHeight="1" s="127">
-      <c r="A28" s="126" t="n">
+      <c r="A28" s="366" t="n">
         <v>9</v>
       </c>
-      <c r="B28" s="72" t="n"/>
-      <c r="C28" s="72" t="n"/>
-      <c r="D28" s="72" t="n"/>
-      <c r="E28" s="126" t="n"/>
-      <c r="F28" s="126" t="n"/>
-      <c r="G28" s="126">
+      <c r="B28" s="364" t="n"/>
+      <c r="C28" s="364" t="n"/>
+      <c r="D28" s="364" t="n"/>
+      <c r="E28" s="367" t="n"/>
+      <c r="F28" s="367" t="n"/>
+      <c r="G28" s="366">
         <f>IF(OR(E28="",F28=""),"",IF(E28*F28&gt;=6,"Alto",IF(E28*F28&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H28" s="72" t="n"/>
-      <c r="I28" s="89" t="n"/>
-      <c r="J28" s="72" t="n"/>
-      <c r="K28" s="126" t="n"/>
+      <c r="H28" s="364" t="n"/>
+      <c r="I28" s="362" t="n"/>
+      <c r="J28" s="364" t="n"/>
+      <c r="K28" s="367" t="n"/>
     </row>
     <row r="29" ht="28.05" customHeight="1" s="127">
-      <c r="A29" s="126" t="n">
+      <c r="A29" s="366" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="72" t="n"/>
-      <c r="C29" s="72" t="n"/>
-      <c r="D29" s="72" t="n"/>
-      <c r="E29" s="126" t="n"/>
-      <c r="F29" s="126" t="n"/>
-      <c r="G29" s="126">
+      <c r="B29" s="364" t="n"/>
+      <c r="C29" s="364" t="n"/>
+      <c r="D29" s="364" t="n"/>
+      <c r="E29" s="367" t="n"/>
+      <c r="F29" s="367" t="n"/>
+      <c r="G29" s="366">
         <f>IF(OR(E29="",F29=""),"",IF(E29*F29&gt;=6,"Alto",IF(E29*F29&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H29" s="72" t="n"/>
-      <c r="I29" s="89" t="n"/>
-      <c r="J29" s="72" t="n"/>
-      <c r="K29" s="126" t="n"/>
+      <c r="H29" s="364" t="n"/>
+      <c r="I29" s="362" t="n"/>
+      <c r="J29" s="364" t="n"/>
+      <c r="K29" s="367" t="n"/>
     </row>
     <row r="30" ht="28.05" customHeight="1" s="127">
-      <c r="A30" s="126" t="n">
+      <c r="A30" s="366" t="n">
         <v>11</v>
       </c>
-      <c r="B30" s="72" t="n"/>
-      <c r="C30" s="72" t="n"/>
-      <c r="D30" s="72" t="n"/>
-      <c r="E30" s="126" t="n"/>
-      <c r="F30" s="126" t="n"/>
-      <c r="G30" s="126">
+      <c r="B30" s="364" t="n"/>
+      <c r="C30" s="364" t="n"/>
+      <c r="D30" s="364" t="n"/>
+      <c r="E30" s="367" t="n"/>
+      <c r="F30" s="367" t="n"/>
+      <c r="G30" s="366">
         <f>IF(OR(E30="",F30=""),"",IF(E30*F30&gt;=6,"Alto",IF(E30*F30&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H30" s="72" t="n"/>
-      <c r="I30" s="89" t="n"/>
-      <c r="J30" s="72" t="n"/>
-      <c r="K30" s="126" t="n"/>
+      <c r="H30" s="364" t="n"/>
+      <c r="I30" s="362" t="n"/>
+      <c r="J30" s="364" t="n"/>
+      <c r="K30" s="367" t="n"/>
     </row>
     <row r="31" ht="28.05" customHeight="1" s="127">
-      <c r="A31" s="126" t="n">
+      <c r="A31" s="366" t="n">
         <v>12</v>
       </c>
-      <c r="B31" s="72" t="n"/>
-      <c r="C31" s="72" t="n"/>
-      <c r="D31" s="72" t="n"/>
-      <c r="E31" s="126" t="n"/>
-      <c r="F31" s="126" t="n"/>
-      <c r="G31" s="126">
+      <c r="B31" s="364" t="n"/>
+      <c r="C31" s="364" t="n"/>
+      <c r="D31" s="364" t="n"/>
+      <c r="E31" s="367" t="n"/>
+      <c r="F31" s="367" t="n"/>
+      <c r="G31" s="366">
         <f>IF(OR(E31="",F31=""),"",IF(E31*F31&gt;=6,"Alto",IF(E31*F31&gt;=3,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="H31" s="72" t="n"/>
-      <c r="I31" s="89" t="n"/>
-      <c r="J31" s="72" t="n"/>
-      <c r="K31" s="126" t="n"/>
+      <c r="H31" s="364" t="n"/>
+      <c r="I31" s="362" t="n"/>
+      <c r="J31" s="364" t="n"/>
+      <c r="K31" s="367" t="n"/>
     </row>
     <row r="32" ht="16.5" customHeight="1" s="127">
       <c r="A32" s="227" t="inlineStr">
@@ -3032,27 +3089,27 @@
       <c r="K33" s="350" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="127">
-      <c r="A34" s="230" t="inlineStr">
+      <c r="A34" s="368" t="inlineStr">
         <is>
           <t>☐ Casco de seguridad</t>
         </is>
       </c>
       <c r="B34" s="98" t="n"/>
       <c r="C34" s="97" t="n"/>
-      <c r="D34" s="230" t="inlineStr">
+      <c r="D34" s="368" t="inlineStr">
         <is>
           <t>☐ Gafas de seguridad</t>
         </is>
       </c>
       <c r="E34" s="98" t="n"/>
       <c r="F34" s="97" t="n"/>
-      <c r="G34" s="230" t="inlineStr">
+      <c r="G34" s="368" t="inlineStr">
         <is>
           <t>☐ Guantes de seguridad</t>
         </is>
       </c>
       <c r="H34" s="97" t="n"/>
-      <c r="I34" s="230" t="inlineStr">
+      <c r="I34" s="368" t="inlineStr">
         <is>
           <t>☐ Botas de seguridad</t>
         </is>
@@ -3061,27 +3118,27 @@
       <c r="K34" s="97" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1" s="127">
-      <c r="A35" s="72" t="inlineStr">
+      <c r="A35" s="369" t="inlineStr">
         <is>
           <t>☐ Arnés y línea de vida</t>
         </is>
       </c>
       <c r="B35" s="93" t="n"/>
       <c r="C35" s="89" t="n"/>
-      <c r="D35" s="72" t="inlineStr">
+      <c r="D35" s="369" t="inlineStr">
         <is>
           <t>☐ Protección auditiva</t>
         </is>
       </c>
       <c r="E35" s="93" t="n"/>
       <c r="F35" s="89" t="n"/>
-      <c r="G35" s="72" t="inlineStr">
+      <c r="G35" s="369" t="inlineStr">
         <is>
           <t>☐ Respirador / mascarilla</t>
         </is>
       </c>
       <c r="H35" s="89" t="n"/>
-      <c r="I35" s="72" t="inlineStr">
+      <c r="I35" s="369" t="inlineStr">
         <is>
           <t>☐ Chaleco reflectivo</t>
         </is>
@@ -3090,27 +3147,27 @@
       <c r="K35" s="89" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1" s="127">
-      <c r="A36" s="72" t="inlineStr">
+      <c r="A36" s="369" t="inlineStr">
         <is>
           <t>☐ Careta o protector facial</t>
         </is>
       </c>
       <c r="B36" s="93" t="n"/>
       <c r="C36" s="89" t="n"/>
-      <c r="D36" s="72" t="inlineStr">
+      <c r="D36" s="369" t="inlineStr">
         <is>
           <t>☐ Overol / ropa de trabajo</t>
         </is>
       </c>
       <c r="E36" s="93" t="n"/>
       <c r="F36" s="89" t="n"/>
-      <c r="G36" s="72" t="inlineStr">
+      <c r="G36" s="369" t="inlineStr">
         <is>
           <t>☐ Impermeable</t>
         </is>
       </c>
       <c r="H36" s="89" t="n"/>
-      <c r="I36" s="72" t="inlineStr">
+      <c r="I36" s="369" t="inlineStr">
         <is>
           <t>☐ Otro: ____________</t>
         </is>
@@ -3136,27 +3193,27 @@
       <c r="K37" s="89" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="127">
-      <c r="A38" s="72" t="inlineStr">
+      <c r="A38" s="369" t="inlineStr">
         <is>
           <t>☐ Permiso de alturas</t>
         </is>
       </c>
       <c r="B38" s="93" t="n"/>
       <c r="C38" s="89" t="n"/>
-      <c r="D38" s="72" t="inlineStr">
+      <c r="D38" s="369" t="inlineStr">
         <is>
           <t>☐ Permiso en caliente</t>
         </is>
       </c>
       <c r="E38" s="93" t="n"/>
       <c r="F38" s="89" t="n"/>
-      <c r="G38" s="72" t="inlineStr">
+      <c r="G38" s="369" t="inlineStr">
         <is>
           <t>☐ Espacios confinados</t>
         </is>
       </c>
       <c r="H38" s="89" t="n"/>
-      <c r="I38" s="72" t="inlineStr">
+      <c r="I38" s="369" t="inlineStr">
         <is>
           <t>☐ Excavaciones</t>
         </is>
@@ -3165,27 +3222,27 @@
       <c r="K38" s="89" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1" s="127">
-      <c r="A39" s="72" t="inlineStr">
+      <c r="A39" s="369" t="inlineStr">
         <is>
           <t>☐ Bloqueo y etiquetado (LOTO)</t>
         </is>
       </c>
       <c r="B39" s="93" t="n"/>
       <c r="C39" s="89" t="n"/>
-      <c r="D39" s="72" t="inlineStr">
+      <c r="D39" s="369" t="inlineStr">
         <is>
           <t>☐ Plan de izaje</t>
         </is>
       </c>
       <c r="E39" s="93" t="n"/>
       <c r="F39" s="89" t="n"/>
-      <c r="G39" s="72" t="inlineStr">
+      <c r="G39" s="369" t="inlineStr">
         <is>
           <t>☐ Ninguno</t>
         </is>
       </c>
       <c r="H39" s="89" t="n"/>
-      <c r="I39" s="72" t="inlineStr">
+      <c r="I39" s="369" t="inlineStr">
         <is>
           <t>☐ Otro: ____________</t>
         </is>
@@ -3256,121 +3313,121 @@
       <c r="K42" s="97" t="n"/>
     </row>
     <row r="43" ht="19.05" customHeight="1" s="127">
-      <c r="A43" s="126" t="n">
+      <c r="A43" s="366" t="n">
         <v>1</v>
       </c>
-      <c r="B43" s="76" t="n"/>
-      <c r="C43" s="76" t="n"/>
-      <c r="D43" s="76" t="n"/>
-      <c r="E43" s="76" t="n"/>
-      <c r="F43" s="93" t="n"/>
-      <c r="G43" s="93" t="n"/>
-      <c r="H43" s="89" t="n"/>
+      <c r="B43" s="364" t="n"/>
+      <c r="C43" s="364" t="n"/>
+      <c r="D43" s="364" t="n"/>
+      <c r="E43" s="364" t="n"/>
+      <c r="F43" s="361" t="n"/>
+      <c r="G43" s="361" t="n"/>
+      <c r="H43" s="362" t="n"/>
       <c r="I43" s="120" t="n"/>
       <c r="J43" s="93" t="n"/>
       <c r="K43" s="89" t="n"/>
     </row>
     <row r="44" ht="19.05" customHeight="1" s="127">
-      <c r="A44" s="126" t="n">
+      <c r="A44" s="366" t="n">
         <v>2</v>
       </c>
-      <c r="B44" s="76" t="n"/>
-      <c r="C44" s="76" t="n"/>
-      <c r="D44" s="76" t="n"/>
-      <c r="E44" s="76" t="n"/>
-      <c r="F44" s="93" t="n"/>
-      <c r="G44" s="93" t="n"/>
-      <c r="H44" s="89" t="n"/>
+      <c r="B44" s="364" t="n"/>
+      <c r="C44" s="364" t="n"/>
+      <c r="D44" s="364" t="n"/>
+      <c r="E44" s="364" t="n"/>
+      <c r="F44" s="361" t="n"/>
+      <c r="G44" s="361" t="n"/>
+      <c r="H44" s="362" t="n"/>
       <c r="I44" s="120" t="n"/>
       <c r="J44" s="93" t="n"/>
       <c r="K44" s="89" t="n"/>
     </row>
     <row r="45" ht="19.05" customHeight="1" s="127">
-      <c r="A45" s="126" t="n">
+      <c r="A45" s="366" t="n">
         <v>3</v>
       </c>
-      <c r="B45" s="76" t="n"/>
-      <c r="C45" s="76" t="n"/>
-      <c r="D45" s="76" t="n"/>
-      <c r="E45" s="76" t="n"/>
-      <c r="F45" s="93" t="n"/>
-      <c r="G45" s="93" t="n"/>
-      <c r="H45" s="89" t="n"/>
+      <c r="B45" s="364" t="n"/>
+      <c r="C45" s="364" t="n"/>
+      <c r="D45" s="364" t="n"/>
+      <c r="E45" s="364" t="n"/>
+      <c r="F45" s="361" t="n"/>
+      <c r="G45" s="361" t="n"/>
+      <c r="H45" s="362" t="n"/>
       <c r="I45" s="120" t="n"/>
       <c r="J45" s="93" t="n"/>
       <c r="K45" s="89" t="n"/>
     </row>
     <row r="46" ht="19.05" customHeight="1" s="127">
-      <c r="A46" s="126" t="n">
+      <c r="A46" s="366" t="n">
         <v>4</v>
       </c>
-      <c r="B46" s="76" t="n"/>
-      <c r="C46" s="76" t="n"/>
-      <c r="D46" s="76" t="n"/>
-      <c r="E46" s="76" t="n"/>
-      <c r="F46" s="93" t="n"/>
-      <c r="G46" s="93" t="n"/>
-      <c r="H46" s="89" t="n"/>
+      <c r="B46" s="364" t="n"/>
+      <c r="C46" s="364" t="n"/>
+      <c r="D46" s="364" t="n"/>
+      <c r="E46" s="364" t="n"/>
+      <c r="F46" s="361" t="n"/>
+      <c r="G46" s="361" t="n"/>
+      <c r="H46" s="362" t="n"/>
       <c r="I46" s="120" t="n"/>
       <c r="J46" s="93" t="n"/>
       <c r="K46" s="89" t="n"/>
     </row>
     <row r="47" ht="19.05" customHeight="1" s="127">
-      <c r="A47" s="126" t="n">
+      <c r="A47" s="366" t="n">
         <v>5</v>
       </c>
-      <c r="B47" s="76" t="n"/>
-      <c r="C47" s="76" t="n"/>
-      <c r="D47" s="76" t="n"/>
-      <c r="E47" s="76" t="n"/>
-      <c r="F47" s="93" t="n"/>
-      <c r="G47" s="93" t="n"/>
-      <c r="H47" s="89" t="n"/>
+      <c r="B47" s="364" t="n"/>
+      <c r="C47" s="364" t="n"/>
+      <c r="D47" s="364" t="n"/>
+      <c r="E47" s="364" t="n"/>
+      <c r="F47" s="361" t="n"/>
+      <c r="G47" s="361" t="n"/>
+      <c r="H47" s="362" t="n"/>
       <c r="I47" s="120" t="n"/>
       <c r="J47" s="93" t="n"/>
       <c r="K47" s="89" t="n"/>
     </row>
     <row r="48" ht="19.05" customHeight="1" s="127">
-      <c r="A48" s="126" t="n">
+      <c r="A48" s="366" t="n">
         <v>6</v>
       </c>
-      <c r="B48" s="76" t="n"/>
-      <c r="C48" s="76" t="n"/>
-      <c r="D48" s="76" t="n"/>
-      <c r="E48" s="76" t="n"/>
-      <c r="F48" s="93" t="n"/>
-      <c r="G48" s="93" t="n"/>
-      <c r="H48" s="89" t="n"/>
+      <c r="B48" s="364" t="n"/>
+      <c r="C48" s="364" t="n"/>
+      <c r="D48" s="364" t="n"/>
+      <c r="E48" s="364" t="n"/>
+      <c r="F48" s="361" t="n"/>
+      <c r="G48" s="361" t="n"/>
+      <c r="H48" s="362" t="n"/>
       <c r="I48" s="120" t="n"/>
       <c r="J48" s="93" t="n"/>
       <c r="K48" s="89" t="n"/>
     </row>
     <row r="49" ht="19.05" customHeight="1" s="127">
-      <c r="A49" s="126" t="n">
+      <c r="A49" s="366" t="n">
         <v>7</v>
       </c>
-      <c r="B49" s="76" t="n"/>
-      <c r="C49" s="76" t="n"/>
-      <c r="D49" s="76" t="n"/>
-      <c r="E49" s="76" t="n"/>
-      <c r="F49" s="93" t="n"/>
-      <c r="G49" s="93" t="n"/>
-      <c r="H49" s="89" t="n"/>
+      <c r="B49" s="364" t="n"/>
+      <c r="C49" s="364" t="n"/>
+      <c r="D49" s="364" t="n"/>
+      <c r="E49" s="364" t="n"/>
+      <c r="F49" s="361" t="n"/>
+      <c r="G49" s="361" t="n"/>
+      <c r="H49" s="362" t="n"/>
       <c r="I49" s="120" t="n"/>
       <c r="J49" s="93" t="n"/>
       <c r="K49" s="89" t="n"/>
     </row>
     <row r="50" ht="19.05" customHeight="1" s="127">
-      <c r="A50" s="126" t="n">
+      <c r="A50" s="366" t="n">
         <v>8</v>
       </c>
-      <c r="B50" s="76" t="n"/>
-      <c r="C50" s="76" t="n"/>
-      <c r="D50" s="76" t="n"/>
-      <c r="E50" s="76" t="n"/>
-      <c r="F50" s="93" t="n"/>
-      <c r="G50" s="93" t="n"/>
-      <c r="H50" s="89" t="n"/>
+      <c r="B50" s="364" t="n"/>
+      <c r="C50" s="364" t="n"/>
+      <c r="D50" s="364" t="n"/>
+      <c r="E50" s="364" t="n"/>
+      <c r="F50" s="361" t="n"/>
+      <c r="G50" s="361" t="n"/>
+      <c r="H50" s="362" t="n"/>
       <c r="I50" s="120" t="n"/>
       <c r="J50" s="93" t="n"/>
       <c r="K50" s="89" t="n"/>
@@ -3399,8 +3456,8 @@
         </is>
       </c>
       <c r="B52" s="89" t="n"/>
-      <c r="C52" s="68" t="n"/>
-      <c r="D52" s="89" t="n"/>
+      <c r="C52" s="364" t="n"/>
+      <c r="D52" s="362" t="n"/>
       <c r="E52" s="59" t="inlineStr">
         <is>
           <t>Teléfono de emergencias</t>
@@ -3408,7 +3465,7 @@
       </c>
       <c r="F52" s="93" t="n"/>
       <c r="G52" s="89" t="n"/>
-      <c r="H52" s="68" t="n"/>
+      <c r="H52" s="364" t="n"/>
       <c r="I52" s="59" t="inlineStr">
         <is>
           <t>Brigadista</t>
@@ -3424,8 +3481,8 @@
         </is>
       </c>
       <c r="B53" s="89" t="n"/>
-      <c r="C53" s="68" t="n"/>
-      <c r="D53" s="89" t="n"/>
+      <c r="C53" s="364" t="n"/>
+      <c r="D53" s="362" t="n"/>
       <c r="E53" s="59" t="inlineStr">
         <is>
           <t>Ruta de evacuación o rescate</t>
@@ -3433,10 +3490,10 @@
       </c>
       <c r="F53" s="93" t="n"/>
       <c r="G53" s="89" t="n"/>
-      <c r="H53" s="68" t="n"/>
-      <c r="I53" s="93" t="n"/>
-      <c r="J53" s="93" t="n"/>
-      <c r="K53" s="89" t="n"/>
+      <c r="H53" s="364" t="n"/>
+      <c r="I53" s="361" t="n"/>
+      <c r="J53" s="361" t="n"/>
+      <c r="K53" s="362" t="n"/>
     </row>
     <row r="54" ht="16.5" customHeight="1" s="127">
       <c r="A54" s="227" t="inlineStr">
@@ -3478,23 +3535,23 @@
         </is>
       </c>
       <c r="B56" s="97" t="n"/>
-      <c r="C56" s="301" t="n"/>
+      <c r="C56" s="370" t="n"/>
       <c r="D56" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="E56" s="97" t="n"/>
-      <c r="F56" s="301" t="n"/>
-      <c r="G56" s="97" t="n"/>
+      <c r="F56" s="370" t="n"/>
+      <c r="G56" s="371" t="n"/>
       <c r="H56" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="I56" s="354" t="n"/>
-      <c r="J56" s="98" t="n"/>
-      <c r="K56" s="97" t="n"/>
+      <c r="I56" s="372" t="n"/>
+      <c r="J56" s="373" t="n"/>
+      <c r="K56" s="371" t="n"/>
     </row>
     <row r="57" ht="21" customHeight="1" s="127">
       <c r="A57" s="70" t="inlineStr">
@@ -3503,23 +3560,23 @@
         </is>
       </c>
       <c r="B57" s="89" t="n"/>
-      <c r="C57" s="68" t="n"/>
+      <c r="C57" s="364" t="n"/>
       <c r="D57" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="E57" s="89" t="n"/>
-      <c r="F57" s="68" t="n"/>
-      <c r="G57" s="89" t="n"/>
+      <c r="F57" s="364" t="n"/>
+      <c r="G57" s="362" t="n"/>
       <c r="H57" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="I57" s="355" t="n"/>
-      <c r="J57" s="93" t="n"/>
-      <c r="K57" s="89" t="n"/>
+      <c r="I57" s="363" t="n"/>
+      <c r="J57" s="361" t="n"/>
+      <c r="K57" s="362" t="n"/>
     </row>
     <row r="58" ht="21" customHeight="1" s="127">
       <c r="A58" s="70" t="inlineStr">
@@ -3528,23 +3585,23 @@
         </is>
       </c>
       <c r="B58" s="89" t="n"/>
-      <c r="C58" s="68" t="n"/>
+      <c r="C58" s="364" t="n"/>
       <c r="D58" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="E58" s="89" t="n"/>
-      <c r="F58" s="68" t="n"/>
-      <c r="G58" s="89" t="n"/>
+      <c r="F58" s="364" t="n"/>
+      <c r="G58" s="362" t="n"/>
       <c r="H58" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="I58" s="355" t="n"/>
-      <c r="J58" s="93" t="n"/>
-      <c r="K58" s="89" t="n"/>
+      <c r="I58" s="363" t="n"/>
+      <c r="J58" s="361" t="n"/>
+      <c r="K58" s="362" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="25" t="inlineStr">
@@ -3558,6 +3615,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="116">
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C15:D15"/>
